--- a/outputs/46121.xlsx
+++ b/outputs/46121.xlsx
@@ -153,11 +153,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="166" formatCode="\$#,##0.00"/>
-    <numFmt numFmtId="167" formatCode="\$#,##0.00"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -334,128 +333,116 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="28">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2078,54 +2065,54 @@
         <v>11</v>
       </c>
       <c r="B5" s="15" t="n">
-        <f aca="false">SUMIFS(Transactions!C:C,Transactions!D:D,$A5,Transactions!A:A,B$3)</f>
+        <f aca="false">SUMIFS(Transactions!$C:$C,Transactions!$A:$A,B$3,Transactions!$D:$D,$A5)</f>
         <v>0</v>
       </c>
       <c r="C5" s="15" t="n">
-        <f aca="false">SUMIFS(Transactions!C:C,Transactions!D:D,$A5,Transactions!A:A,C$3)</f>
+        <f aca="false">SUMIFS(Transactions!$C:$C,Transactions!$A:$A,C$3,Transactions!$D:$D,$A5)</f>
         <v>0</v>
       </c>
       <c r="D5" s="16" t="n">
-        <f aca="false">SUMIFS(Transactions!C:C,Transactions!D:D,$A5,Transactions!A:A,D$3)</f>
+        <f aca="false">SUMIFS(Transactions!$C:$C,Transactions!$A:$A,D$3,Transactions!$D:$D,$A5)</f>
         <v>0</v>
       </c>
       <c r="E5" s="15" t="n">
-        <f aca="false">SUMIFS(Transactions!C:C,Transactions!D:D,$A5,Transactions!A:A,E$3)</f>
+        <f aca="false">SUMIFS(Transactions!$C:$C,Transactions!$A:$A,E$3,Transactions!$D:$D,$A5)</f>
         <v>0</v>
       </c>
       <c r="F5" s="15" t="n">
-        <f aca="false">SUMIFS(Transactions!C:C,Transactions!D:D,$A5,Transactions!A:A,F$3)</f>
+        <f aca="false">SUMIFS(Transactions!$C:$C,Transactions!$A:$A,F$3,Transactions!$D:$D,$A5)</f>
         <v>0</v>
       </c>
       <c r="G5" s="15" t="n">
-        <f aca="false">SUMIFS(Transactions!C:C,Transactions!D:D,$A5,Transactions!A:A,G$3)</f>
+        <f aca="false">SUMIFS(Transactions!$C:$C,Transactions!$A:$A,G$3,Transactions!$D:$D,$A5)</f>
         <v>0</v>
       </c>
       <c r="H5" s="15" t="n">
-        <f aca="false">SUMIFS(Transactions!C:C,Transactions!D:D,$A5,Transactions!A:A,H$3)</f>
+        <f aca="false">SUMIFS(Transactions!$C:$C,Transactions!$A:$A,H$3,Transactions!$D:$D,$A5)</f>
         <v>0</v>
       </c>
       <c r="I5" s="15" t="n">
-        <f aca="false">SUMIFS(Transactions!C:C,Transactions!D:D,$A5,Transactions!A:A,I$3)</f>
+        <f aca="false">SUMIFS(Transactions!$C:$C,Transactions!$A:$A,I$3,Transactions!$D:$D,$A5)</f>
         <v>0</v>
       </c>
       <c r="J5" s="15" t="n">
-        <f aca="false">SUMIFS(Transactions!C:C,Transactions!D:D,$A5,Transactions!A:A,J$3)</f>
+        <f aca="false">SUMIFS(Transactions!$C:$C,Transactions!$A:$A,J$3,Transactions!$D:$D,$A5)</f>
         <v>0</v>
       </c>
       <c r="K5" s="15" t="n">
-        <f aca="false">SUMIFS(Transactions!C:C,Transactions!D:D,$A5,Transactions!A:A,K$3)</f>
+        <f aca="false">SUMIFS(Transactions!$C:$C,Transactions!$A:$A,K$3,Transactions!$D:$D,$A5)</f>
         <v>0</v>
       </c>
       <c r="L5" s="15" t="n">
-        <f aca="false">SUMIFS(Transactions!C:C,Transactions!D:D,$A5,Transactions!A:A,L$3)</f>
+        <f aca="false">SUMIFS(Transactions!$C:$C,Transactions!$A:$A,L$3,Transactions!$D:$D,$A5)</f>
         <v>0</v>
       </c>
       <c r="M5" s="15" t="n">
-        <f aca="false">SUMIFS(Transactions!C:C,Transactions!D:D,$A5,Transactions!A:A,M$3)</f>
-        <v>0</v>
-      </c>
-      <c r="N5" s="17" t="n">
+        <f aca="false">SUMIFS(Transactions!$C:$C,Transactions!$A:$A,M$3,Transactions!$D:$D,$A5)</f>
+        <v>0</v>
+      </c>
+      <c r="N5" s="15" t="n">
         <f aca="false">SUM(B5:M5)</f>
         <v>0</v>
       </c>
@@ -2135,54 +2122,54 @@
         <v>12</v>
       </c>
       <c r="B6" s="16" t="n">
-        <f aca="false">SUMIFS(Transactions!C:C,Transactions!D:D,$A6,Transactions!A:A,B$3)</f>
+        <f aca="false">SUMIFS(Transactions!$C:$C,Transactions!$A:$A,B$3,Transactions!$D:$D,$A6)</f>
         <v>0</v>
       </c>
       <c r="C6" s="15" t="n">
-        <f aca="false">SUMIFS(Transactions!C:C,Transactions!D:D,$A6,Transactions!A:A,C$3)</f>
+        <f aca="false">SUMIFS(Transactions!$C:$C,Transactions!$A:$A,C$3,Transactions!$D:$D,$A6)</f>
         <v>0</v>
       </c>
       <c r="D6" s="16" t="n">
-        <f aca="false">SUMIFS(Transactions!C:C,Transactions!D:D,$A6,Transactions!A:A,D$3)</f>
+        <f aca="false">SUMIFS(Transactions!$C:$C,Transactions!$A:$A,D$3,Transactions!$D:$D,$A6)</f>
         <v>0</v>
       </c>
       <c r="E6" s="15" t="n">
-        <f aca="false">SUMIFS(Transactions!C:C,Transactions!D:D,$A6,Transactions!A:A,E$3)</f>
+        <f aca="false">SUMIFS(Transactions!$C:$C,Transactions!$A:$A,E$3,Transactions!$D:$D,$A6)</f>
         <v>0</v>
       </c>
       <c r="F6" s="15" t="n">
-        <f aca="false">SUMIFS(Transactions!C:C,Transactions!D:D,$A6,Transactions!A:A,F$3)</f>
+        <f aca="false">SUMIFS(Transactions!$C:$C,Transactions!$A:$A,F$3,Transactions!$D:$D,$A6)</f>
         <v>0</v>
       </c>
       <c r="G6" s="15" t="n">
-        <f aca="false">SUMIFS(Transactions!C:C,Transactions!D:D,$A6,Transactions!A:A,G$3)</f>
+        <f aca="false">SUMIFS(Transactions!$C:$C,Transactions!$A:$A,G$3,Transactions!$D:$D,$A6)</f>
         <v>0</v>
       </c>
       <c r="H6" s="15" t="n">
-        <f aca="false">SUMIFS(Transactions!C:C,Transactions!D:D,$A6,Transactions!A:A,H$3)</f>
+        <f aca="false">SUMIFS(Transactions!$C:$C,Transactions!$A:$A,H$3,Transactions!$D:$D,$A6)</f>
         <v>0</v>
       </c>
       <c r="I6" s="15" t="n">
-        <f aca="false">SUMIFS(Transactions!C:C,Transactions!D:D,$A6,Transactions!A:A,I$3)</f>
+        <f aca="false">SUMIFS(Transactions!$C:$C,Transactions!$A:$A,I$3,Transactions!$D:$D,$A6)</f>
         <v>0</v>
       </c>
       <c r="J6" s="15" t="n">
-        <f aca="false">SUMIFS(Transactions!C:C,Transactions!D:D,$A6,Transactions!A:A,J$3)</f>
+        <f aca="false">SUMIFS(Transactions!$C:$C,Transactions!$A:$A,J$3,Transactions!$D:$D,$A6)</f>
         <v>0</v>
       </c>
       <c r="K6" s="15" t="n">
-        <f aca="false">SUMIFS(Transactions!C:C,Transactions!D:D,$A6,Transactions!A:A,K$3)</f>
+        <f aca="false">SUMIFS(Transactions!$C:$C,Transactions!$A:$A,K$3,Transactions!$D:$D,$A6)</f>
         <v>0</v>
       </c>
       <c r="L6" s="15" t="n">
-        <f aca="false">SUMIFS(Transactions!C:C,Transactions!D:D,$A6,Transactions!A:A,L$3)</f>
+        <f aca="false">SUMIFS(Transactions!$C:$C,Transactions!$A:$A,L$3,Transactions!$D:$D,$A6)</f>
         <v>0</v>
       </c>
       <c r="M6" s="15" t="n">
-        <f aca="false">SUMIFS(Transactions!C:C,Transactions!D:D,$A6,Transactions!A:A,M$3)</f>
-        <v>0</v>
-      </c>
-      <c r="N6" s="17" t="n">
+        <f aca="false">SUMIFS(Transactions!$C:$C,Transactions!$A:$A,M$3,Transactions!$D:$D,$A6)</f>
+        <v>0</v>
+      </c>
+      <c r="N6" s="15" t="n">
         <f aca="false">SUM(B6:M6)</f>
         <v>0</v>
       </c>
@@ -2192,205 +2179,205 @@
         <v>10</v>
       </c>
       <c r="B7" s="15" t="n">
-        <f aca="false">SUMIFS(Transactions!C:C,Transactions!D:D,$A7,Transactions!A:A,B$3)</f>
+        <f aca="false">SUMIFS(Transactions!$C:$C,Transactions!$A:$A,B$3,Transactions!$D:$D,$A7)</f>
         <v>0</v>
       </c>
       <c r="C7" s="15" t="n">
-        <f aca="false">SUMIFS(Transactions!C:C,Transactions!D:D,$A7,Transactions!A:A,C$3)</f>
+        <f aca="false">SUMIFS(Transactions!$C:$C,Transactions!$A:$A,C$3,Transactions!$D:$D,$A7)</f>
         <v>0</v>
       </c>
       <c r="D7" s="15" t="n">
-        <f aca="false">SUMIFS(Transactions!C:C,Transactions!D:D,$A7,Transactions!A:A,D$3)</f>
+        <f aca="false">SUMIFS(Transactions!$C:$C,Transactions!$A:$A,D$3,Transactions!$D:$D,$A7)</f>
         <v>80</v>
       </c>
       <c r="E7" s="15" t="n">
-        <f aca="false">SUMIFS(Transactions!C:C,Transactions!D:D,$A7,Transactions!A:A,E$3)</f>
+        <f aca="false">SUMIFS(Transactions!$C:$C,Transactions!$A:$A,E$3,Transactions!$D:$D,$A7)</f>
         <v>10</v>
       </c>
       <c r="F7" s="15" t="n">
-        <f aca="false">SUMIFS(Transactions!C:C,Transactions!D:D,$A7,Transactions!A:A,F$3)</f>
+        <f aca="false">SUMIFS(Transactions!$C:$C,Transactions!$A:$A,F$3,Transactions!$D:$D,$A7)</f>
         <v>0</v>
       </c>
       <c r="G7" s="15" t="n">
-        <f aca="false">SUMIFS(Transactions!C:C,Transactions!D:D,$A7,Transactions!A:A,G$3)</f>
+        <f aca="false">SUMIFS(Transactions!$C:$C,Transactions!$A:$A,G$3,Transactions!$D:$D,$A7)</f>
         <v>0</v>
       </c>
       <c r="H7" s="15" t="n">
-        <f aca="false">SUMIFS(Transactions!C:C,Transactions!D:D,$A7,Transactions!A:A,H$3)</f>
+        <f aca="false">SUMIFS(Transactions!$C:$C,Transactions!$A:$A,H$3,Transactions!$D:$D,$A7)</f>
         <v>0</v>
       </c>
       <c r="I7" s="15" t="n">
-        <f aca="false">SUMIFS(Transactions!C:C,Transactions!D:D,$A7,Transactions!A:A,I$3)</f>
+        <f aca="false">SUMIFS(Transactions!$C:$C,Transactions!$A:$A,I$3,Transactions!$D:$D,$A7)</f>
         <v>0</v>
       </c>
       <c r="J7" s="15" t="n">
-        <f aca="false">SUMIFS(Transactions!C:C,Transactions!D:D,$A7,Transactions!A:A,J$3)</f>
+        <f aca="false">SUMIFS(Transactions!$C:$C,Transactions!$A:$A,J$3,Transactions!$D:$D,$A7)</f>
         <v>0</v>
       </c>
       <c r="K7" s="15" t="n">
-        <f aca="false">SUMIFS(Transactions!C:C,Transactions!D:D,$A7,Transactions!A:A,K$3)</f>
+        <f aca="false">SUMIFS(Transactions!$C:$C,Transactions!$A:$A,K$3,Transactions!$D:$D,$A7)</f>
         <v>0</v>
       </c>
       <c r="L7" s="15" t="n">
-        <f aca="false">SUMIFS(Transactions!C:C,Transactions!D:D,$A7,Transactions!A:A,L$3)</f>
+        <f aca="false">SUMIFS(Transactions!$C:$C,Transactions!$A:$A,L$3,Transactions!$D:$D,$A7)</f>
         <v>0</v>
       </c>
       <c r="M7" s="15" t="n">
-        <f aca="false">SUMIFS(Transactions!C:C,Transactions!D:D,$A7,Transactions!A:A,M$3)</f>
-        <v>0</v>
-      </c>
-      <c r="N7" s="17" t="n">
+        <f aca="false">SUMIFS(Transactions!$C:$C,Transactions!$A:$A,M$3,Transactions!$D:$D,$A7)</f>
+        <v>0</v>
+      </c>
+      <c r="N7" s="15" t="n">
         <f aca="false">SUM(B7:M7)</f>
         <v>90</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="19" t="n">
-        <f aca="false">SUMIFS(Transactions!C:C,Transactions!D:D,$A8,Transactions!A:A,B$3)</f>
-        <v>0</v>
-      </c>
-      <c r="C8" s="20" t="n">
-        <f aca="false">SUMIFS(Transactions!C:C,Transactions!D:D,$A8,Transactions!A:A,C$3)</f>
-        <v>0</v>
-      </c>
-      <c r="D8" s="20" t="n">
-        <f aca="false">SUMIFS(Transactions!C:C,Transactions!D:D,$A8,Transactions!A:A,D$3)</f>
-        <v>0</v>
-      </c>
-      <c r="E8" s="20" t="n">
-        <f aca="false">SUMIFS(Transactions!C:C,Transactions!D:D,$A8,Transactions!A:A,E$3)</f>
-        <v>0</v>
-      </c>
-      <c r="F8" s="20" t="n">
-        <f aca="false">SUMIFS(Transactions!C:C,Transactions!D:D,$A8,Transactions!A:A,F$3)</f>
-        <v>0</v>
-      </c>
-      <c r="G8" s="20" t="n">
-        <f aca="false">SUMIFS(Transactions!C:C,Transactions!D:D,$A8,Transactions!A:A,G$3)</f>
-        <v>0</v>
-      </c>
-      <c r="H8" s="20" t="n">
-        <f aca="false">SUMIFS(Transactions!C:C,Transactions!D:D,$A8,Transactions!A:A,H$3)</f>
-        <v>0</v>
-      </c>
-      <c r="I8" s="20" t="n">
-        <f aca="false">SUMIFS(Transactions!C:C,Transactions!D:D,$A8,Transactions!A:A,I$3)</f>
-        <v>0</v>
-      </c>
-      <c r="J8" s="20" t="n">
-        <f aca="false">SUMIFS(Transactions!C:C,Transactions!D:D,$A8,Transactions!A:A,J$3)</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="20" t="n">
-        <f aca="false">SUMIFS(Transactions!C:C,Transactions!D:D,$A8,Transactions!A:A,K$3)</f>
-        <v>0</v>
-      </c>
-      <c r="L8" s="20" t="n">
-        <f aca="false">SUMIFS(Transactions!C:C,Transactions!D:D,$A8,Transactions!A:A,L$3)</f>
-        <v>0</v>
-      </c>
-      <c r="M8" s="20" t="n">
-        <f aca="false">SUMIFS(Transactions!C:C,Transactions!D:D,$A8,Transactions!A:A,M$3)</f>
-        <v>0</v>
-      </c>
-      <c r="N8" s="21" t="n">
+      <c r="B8" s="18" t="n">
+        <f aca="false">SUMIFS(Transactions!$C:$C,Transactions!$A:$A,B$3,Transactions!$D:$D,$A8)</f>
+        <v>0</v>
+      </c>
+      <c r="C8" s="19" t="n">
+        <f aca="false">SUMIFS(Transactions!$C:$C,Transactions!$A:$A,C$3,Transactions!$D:$D,$A8)</f>
+        <v>0</v>
+      </c>
+      <c r="D8" s="19" t="n">
+        <f aca="false">SUMIFS(Transactions!$C:$C,Transactions!$A:$A,D$3,Transactions!$D:$D,$A8)</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="19" t="n">
+        <f aca="false">SUMIFS(Transactions!$C:$C,Transactions!$A:$A,E$3,Transactions!$D:$D,$A8)</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="19" t="n">
+        <f aca="false">SUMIFS(Transactions!$C:$C,Transactions!$A:$A,F$3,Transactions!$D:$D,$A8)</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="19" t="n">
+        <f aca="false">SUMIFS(Transactions!$C:$C,Transactions!$A:$A,G$3,Transactions!$D:$D,$A8)</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="19" t="n">
+        <f aca="false">SUMIFS(Transactions!$C:$C,Transactions!$A:$A,H$3,Transactions!$D:$D,$A8)</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="19" t="n">
+        <f aca="false">SUMIFS(Transactions!$C:$C,Transactions!$A:$A,I$3,Transactions!$D:$D,$A8)</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="19" t="n">
+        <f aca="false">SUMIFS(Transactions!$C:$C,Transactions!$A:$A,J$3,Transactions!$D:$D,$A8)</f>
+        <v>0</v>
+      </c>
+      <c r="K8" s="19" t="n">
+        <f aca="false">SUMIFS(Transactions!$C:$C,Transactions!$A:$A,K$3,Transactions!$D:$D,$A8)</f>
+        <v>0</v>
+      </c>
+      <c r="L8" s="19" t="n">
+        <f aca="false">SUMIFS(Transactions!$C:$C,Transactions!$A:$A,L$3,Transactions!$D:$D,$A8)</f>
+        <v>0</v>
+      </c>
+      <c r="M8" s="19" t="n">
+        <f aca="false">SUMIFS(Transactions!$C:$C,Transactions!$A:$A,M$3,Transactions!$D:$D,$A8)</f>
+        <v>0</v>
+      </c>
+      <c r="N8" s="19" t="n">
         <f aca="false">SUM(B8:M8)</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="23" t="n">
+      <c r="B9" s="21" t="n">
         <f aca="false">SUM(B5:B8)</f>
         <v>0</v>
       </c>
-      <c r="C9" s="23" t="n">
+      <c r="C9" s="21" t="n">
         <f aca="false">SUM(C5:C8)</f>
         <v>0</v>
       </c>
-      <c r="D9" s="23" t="n">
+      <c r="D9" s="21" t="n">
         <f aca="false">SUM(D5:D8)</f>
         <v>80</v>
       </c>
-      <c r="E9" s="23" t="n">
+      <c r="E9" s="21" t="n">
         <f aca="false">SUM(E5:E8)</f>
         <v>10</v>
       </c>
-      <c r="F9" s="23" t="n">
+      <c r="F9" s="21" t="n">
         <f aca="false">SUM(F5:F8)</f>
         <v>0</v>
       </c>
-      <c r="G9" s="23" t="n">
+      <c r="G9" s="21" t="n">
         <f aca="false">SUM(G5:G8)</f>
         <v>0</v>
       </c>
-      <c r="H9" s="23" t="n">
+      <c r="H9" s="21" t="n">
         <f aca="false">SUM(H5:H8)</f>
         <v>0</v>
       </c>
-      <c r="I9" s="23" t="n">
+      <c r="I9" s="21" t="n">
         <f aca="false">SUM(I5:I8)</f>
         <v>0</v>
       </c>
-      <c r="J9" s="23" t="n">
+      <c r="J9" s="21" t="n">
         <f aca="false">SUM(J5:J8)</f>
         <v>0</v>
       </c>
-      <c r="K9" s="23" t="n">
+      <c r="K9" s="21" t="n">
         <f aca="false">SUM(K5:K8)</f>
         <v>0</v>
       </c>
-      <c r="L9" s="23" t="n">
+      <c r="L9" s="21" t="n">
         <f aca="false">SUM(L5:L8)</f>
         <v>0</v>
       </c>
-      <c r="M9" s="23" t="n">
+      <c r="M9" s="21" t="n">
         <f aca="false">SUM(M5:M8)</f>
         <v>0</v>
       </c>
-      <c r="N9" s="23" t="n">
+      <c r="N9" s="21" t="n">
         <f aca="false">SUM(N5:N8)</f>
         <v>90</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="17"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="17"/>
-      <c r="L10" s="17"/>
-      <c r="M10" s="17"/>
-      <c r="N10" s="17"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="15"/>
+      <c r="N10" s="15"/>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="24" t="s">
+      <c r="A11" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="25"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="25"/>
-      <c r="H11" s="25"/>
-      <c r="I11" s="25"/>
-      <c r="J11" s="25"/>
-      <c r="K11" s="25"/>
-      <c r="L11" s="25"/>
-      <c r="M11" s="25"/>
-      <c r="N11" s="25"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="23"/>
+      <c r="G11" s="23"/>
+      <c r="H11" s="23"/>
+      <c r="I11" s="23"/>
+      <c r="J11" s="23"/>
+      <c r="K11" s="23"/>
+      <c r="L11" s="23"/>
+      <c r="M11" s="23"/>
+      <c r="N11" s="23"/>
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
@@ -2414,19 +2401,19 @@
       <c r="A13" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="26"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="17"/>
-      <c r="J13" s="17"/>
-      <c r="K13" s="17"/>
-      <c r="L13" s="17"/>
-      <c r="M13" s="17"/>
-      <c r="N13" s="17" t="n">
+      <c r="B13" s="16"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="15"/>
+      <c r="N13" s="15" t="n">
         <f aca="false">SUM(B13:M13)</f>
         <v>0</v>
       </c>
@@ -2435,115 +2422,115 @@
       <c r="A14" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="26"/>
-      <c r="C14" s="26"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="17"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="17"/>
-      <c r="L14" s="17"/>
-      <c r="M14" s="17"/>
-      <c r="N14" s="17" t="n">
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="15" t="n">
         <f aca="false">SUM(B14:M14)</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="22" t="s">
+      <c r="A15" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="23" t="n">
+      <c r="B15" s="21" t="n">
         <f aca="false">SUM(B13:B14)</f>
         <v>0</v>
       </c>
-      <c r="C15" s="23" t="n">
+      <c r="C15" s="21" t="n">
         <f aca="false">SUM(C12:C14)</f>
         <v>0</v>
       </c>
-      <c r="D15" s="23" t="n">
+      <c r="D15" s="21" t="n">
         <f aca="false">SUM(D12:D14)</f>
         <v>0</v>
       </c>
-      <c r="E15" s="23" t="n">
+      <c r="E15" s="21" t="n">
         <f aca="false">SUM(E12:E14)</f>
         <v>0</v>
       </c>
-      <c r="F15" s="23" t="n">
+      <c r="F15" s="21" t="n">
         <f aca="false">SUM(F12:F14)</f>
         <v>0</v>
       </c>
-      <c r="G15" s="23" t="n">
+      <c r="G15" s="21" t="n">
         <f aca="false">SUM(G12:G14)</f>
         <v>0</v>
       </c>
-      <c r="H15" s="23" t="n">
+      <c r="H15" s="21" t="n">
         <f aca="false">SUM(H12:H14)</f>
         <v>0</v>
       </c>
-      <c r="I15" s="23" t="n">
+      <c r="I15" s="21" t="n">
         <f aca="false">SUM(I12:I14)</f>
         <v>0</v>
       </c>
-      <c r="J15" s="23" t="n">
+      <c r="J15" s="21" t="n">
         <f aca="false">SUM(J12:J14)</f>
         <v>0</v>
       </c>
-      <c r="K15" s="23" t="n">
+      <c r="K15" s="21" t="n">
         <f aca="false">SUM(K12:K14)</f>
         <v>0</v>
       </c>
-      <c r="L15" s="23" t="n">
+      <c r="L15" s="21" t="n">
         <f aca="false">SUM(L12:L14)</f>
         <v>0</v>
       </c>
-      <c r="M15" s="23" t="n">
+      <c r="M15" s="21" t="n">
         <f aca="false">SUM(M12:M14)</f>
         <v>0</v>
       </c>
-      <c r="N15" s="23" t="n">
+      <c r="N15" s="21" t="n">
         <f aca="false">SUM(N13:N14)</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="27"/>
-      <c r="B16" s="28"/>
-      <c r="C16" s="28"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="28"/>
-      <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
-      <c r="I16" s="28"/>
-      <c r="J16" s="28"/>
-      <c r="K16" s="28"/>
-      <c r="L16" s="28"/>
-      <c r="M16" s="28"/>
-      <c r="N16" s="28"/>
-      <c r="O16" s="29"/>
-      <c r="P16" s="29"/>
-      <c r="Q16" s="29"/>
-      <c r="R16" s="29"/>
-      <c r="S16" s="29"/>
-      <c r="T16" s="29"/>
-      <c r="U16" s="29"/>
-      <c r="V16" s="29"/>
-      <c r="W16" s="29"/>
-      <c r="X16" s="29"/>
-      <c r="Y16" s="29"/>
-      <c r="Z16" s="29"/>
-      <c r="AA16" s="29"/>
-      <c r="AB16" s="29"/>
-      <c r="AC16" s="29"/>
-      <c r="AD16" s="29"/>
-      <c r="AE16" s="29"/>
-      <c r="AF16" s="29"/>
-      <c r="AG16" s="29"/>
-      <c r="AH16" s="29"/>
+      <c r="A16" s="24"/>
+      <c r="B16" s="25"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="25"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="25"/>
+      <c r="I16" s="25"/>
+      <c r="J16" s="25"/>
+      <c r="K16" s="25"/>
+      <c r="L16" s="25"/>
+      <c r="M16" s="25"/>
+      <c r="N16" s="25"/>
+      <c r="O16" s="26"/>
+      <c r="P16" s="26"/>
+      <c r="Q16" s="26"/>
+      <c r="R16" s="26"/>
+      <c r="S16" s="26"/>
+      <c r="T16" s="26"/>
+      <c r="U16" s="26"/>
+      <c r="V16" s="26"/>
+      <c r="W16" s="26"/>
+      <c r="X16" s="26"/>
+      <c r="Y16" s="26"/>
+      <c r="Z16" s="26"/>
+      <c r="AA16" s="26"/>
+      <c r="AB16" s="26"/>
+      <c r="AC16" s="26"/>
+      <c r="AD16" s="26"/>
+      <c r="AE16" s="26"/>
+      <c r="AF16" s="26"/>
+      <c r="AG16" s="26"/>
+      <c r="AH16" s="26"/>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
@@ -2567,19 +2554,19 @@
       <c r="A18" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="17"/>
-      <c r="C18" s="26"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="17"/>
-      <c r="I18" s="17"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="17"/>
-      <c r="L18" s="17"/>
-      <c r="M18" s="17"/>
-      <c r="N18" s="17" t="n">
+      <c r="B18" s="15"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="15"/>
+      <c r="L18" s="15"/>
+      <c r="M18" s="15"/>
+      <c r="N18" s="15" t="n">
         <f aca="false">SUM(B18:M18)</f>
         <v>0</v>
       </c>
@@ -2588,2725 +2575,2725 @@
       <c r="A19" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="17"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="17"/>
-      <c r="I19" s="17"/>
-      <c r="J19" s="17"/>
-      <c r="K19" s="17"/>
-      <c r="L19" s="17"/>
-      <c r="M19" s="17"/>
-      <c r="N19" s="17" t="n">
+      <c r="B19" s="15"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="15"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="15"/>
+      <c r="L19" s="15"/>
+      <c r="M19" s="15"/>
+      <c r="N19" s="15" t="n">
         <f aca="false">SUM(B19:M19)</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="22" t="s">
+      <c r="A20" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="23" t="n">
+      <c r="B20" s="21" t="n">
         <f aca="false">SUM(B18:B19)</f>
         <v>0</v>
       </c>
-      <c r="C20" s="23" t="n">
+      <c r="C20" s="21" t="n">
         <f aca="false">SUM(C18:C19)</f>
         <v>0</v>
       </c>
-      <c r="D20" s="23" t="n">
+      <c r="D20" s="21" t="n">
         <f aca="false">SUM(D18:D19)</f>
         <v>0</v>
       </c>
-      <c r="E20" s="23" t="n">
+      <c r="E20" s="21" t="n">
         <f aca="false">SUM(E18:E19)</f>
         <v>0</v>
       </c>
-      <c r="F20" s="23" t="n">
+      <c r="F20" s="21" t="n">
         <f aca="false">SUM(F18:F19)</f>
         <v>0</v>
       </c>
-      <c r="G20" s="23" t="n">
+      <c r="G20" s="21" t="n">
         <f aca="false">SUM(G18:G19)</f>
         <v>0</v>
       </c>
-      <c r="H20" s="23" t="n">
+      <c r="H20" s="21" t="n">
         <f aca="false">SUM(H18:H19)</f>
         <v>0</v>
       </c>
-      <c r="I20" s="23" t="n">
+      <c r="I20" s="21" t="n">
         <f aca="false">SUM(I18:I19)</f>
         <v>0</v>
       </c>
-      <c r="J20" s="23" t="n">
+      <c r="J20" s="21" t="n">
         <f aca="false">SUM(J18:J19)</f>
         <v>0</v>
       </c>
-      <c r="K20" s="23" t="n">
+      <c r="K20" s="21" t="n">
         <f aca="false">SUM(K18:K19)</f>
         <v>0</v>
       </c>
-      <c r="L20" s="23" t="n">
+      <c r="L20" s="21" t="n">
         <f aca="false">SUM(L18:L19)</f>
         <v>0</v>
       </c>
-      <c r="M20" s="23" t="n">
+      <c r="M20" s="21" t="n">
         <f aca="false">SUM(M18:M19)</f>
         <v>0</v>
       </c>
-      <c r="N20" s="23" t="n">
+      <c r="N20" s="21" t="n">
         <f aca="false">SUM(N18:N19)</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N21" s="30"/>
+      <c r="N21" s="27"/>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N22" s="30"/>
+      <c r="N22" s="27"/>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N23" s="30"/>
+      <c r="N23" s="27"/>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N24" s="30"/>
+      <c r="N24" s="27"/>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N25" s="30"/>
+      <c r="N25" s="27"/>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N26" s="30"/>
+      <c r="N26" s="27"/>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N27" s="30"/>
+      <c r="N27" s="27"/>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N28" s="30"/>
+      <c r="N28" s="27"/>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N29" s="30"/>
+      <c r="N29" s="27"/>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N30" s="30"/>
+      <c r="N30" s="27"/>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N31" s="30"/>
+      <c r="N31" s="27"/>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N32" s="30"/>
+      <c r="N32" s="27"/>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N33" s="30"/>
+      <c r="N33" s="27"/>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N34" s="30"/>
+      <c r="N34" s="27"/>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N35" s="30"/>
+      <c r="N35" s="27"/>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N36" s="30"/>
+      <c r="N36" s="27"/>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N37" s="30"/>
+      <c r="N37" s="27"/>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N38" s="30"/>
+      <c r="N38" s="27"/>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N39" s="30"/>
+      <c r="N39" s="27"/>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N40" s="30"/>
+      <c r="N40" s="27"/>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N41" s="30"/>
+      <c r="N41" s="27"/>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N42" s="30"/>
+      <c r="N42" s="27"/>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N43" s="30"/>
+      <c r="N43" s="27"/>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N44" s="30"/>
+      <c r="N44" s="27"/>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N45" s="30"/>
+      <c r="N45" s="27"/>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N46" s="30"/>
+      <c r="N46" s="27"/>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N47" s="30"/>
+      <c r="N47" s="27"/>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N48" s="30"/>
+      <c r="N48" s="27"/>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N49" s="30"/>
+      <c r="N49" s="27"/>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N50" s="30"/>
+      <c r="N50" s="27"/>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N51" s="30"/>
+      <c r="N51" s="27"/>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N52" s="30"/>
+      <c r="N52" s="27"/>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N53" s="30"/>
+      <c r="N53" s="27"/>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N54" s="30"/>
+      <c r="N54" s="27"/>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N55" s="30"/>
+      <c r="N55" s="27"/>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N56" s="30"/>
+      <c r="N56" s="27"/>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N57" s="30"/>
+      <c r="N57" s="27"/>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N58" s="30"/>
+      <c r="N58" s="27"/>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N59" s="30"/>
+      <c r="N59" s="27"/>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N60" s="30"/>
+      <c r="N60" s="27"/>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N61" s="30"/>
+      <c r="N61" s="27"/>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N62" s="30"/>
+      <c r="N62" s="27"/>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N63" s="30"/>
+      <c r="N63" s="27"/>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N64" s="30"/>
+      <c r="N64" s="27"/>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N65" s="30"/>
+      <c r="N65" s="27"/>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N66" s="30"/>
+      <c r="N66" s="27"/>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N67" s="30"/>
+      <c r="N67" s="27"/>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N68" s="30"/>
+      <c r="N68" s="27"/>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N69" s="30"/>
+      <c r="N69" s="27"/>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N70" s="30"/>
+      <c r="N70" s="27"/>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N71" s="30"/>
+      <c r="N71" s="27"/>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N72" s="30"/>
+      <c r="N72" s="27"/>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N73" s="30"/>
+      <c r="N73" s="27"/>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N74" s="30"/>
+      <c r="N74" s="27"/>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N75" s="30"/>
+      <c r="N75" s="27"/>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N76" s="30"/>
+      <c r="N76" s="27"/>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N77" s="30"/>
+      <c r="N77" s="27"/>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N78" s="30"/>
+      <c r="N78" s="27"/>
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N79" s="30"/>
+      <c r="N79" s="27"/>
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N80" s="30"/>
+      <c r="N80" s="27"/>
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N81" s="30"/>
+      <c r="N81" s="27"/>
     </row>
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N82" s="30"/>
+      <c r="N82" s="27"/>
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N83" s="30"/>
+      <c r="N83" s="27"/>
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N84" s="30"/>
+      <c r="N84" s="27"/>
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N85" s="30"/>
+      <c r="N85" s="27"/>
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N86" s="30"/>
+      <c r="N86" s="27"/>
     </row>
     <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N87" s="30"/>
+      <c r="N87" s="27"/>
     </row>
     <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N88" s="30"/>
+      <c r="N88" s="27"/>
     </row>
     <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N89" s="30"/>
+      <c r="N89" s="27"/>
     </row>
     <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N90" s="30"/>
+      <c r="N90" s="27"/>
     </row>
     <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N91" s="30"/>
+      <c r="N91" s="27"/>
     </row>
     <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N92" s="30"/>
+      <c r="N92" s="27"/>
     </row>
     <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N93" s="30"/>
+      <c r="N93" s="27"/>
     </row>
     <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N94" s="30"/>
+      <c r="N94" s="27"/>
     </row>
     <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N95" s="30"/>
+      <c r="N95" s="27"/>
     </row>
     <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N96" s="30"/>
+      <c r="N96" s="27"/>
     </row>
     <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N97" s="30"/>
+      <c r="N97" s="27"/>
     </row>
     <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N98" s="30"/>
+      <c r="N98" s="27"/>
     </row>
     <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N99" s="30"/>
+      <c r="N99" s="27"/>
     </row>
     <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N100" s="30"/>
+      <c r="N100" s="27"/>
     </row>
     <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N101" s="30"/>
+      <c r="N101" s="27"/>
     </row>
     <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N102" s="30"/>
+      <c r="N102" s="27"/>
     </row>
     <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N103" s="30"/>
+      <c r="N103" s="27"/>
     </row>
     <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N104" s="30"/>
+      <c r="N104" s="27"/>
     </row>
     <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N105" s="30"/>
+      <c r="N105" s="27"/>
     </row>
     <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N106" s="30"/>
+      <c r="N106" s="27"/>
     </row>
     <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N107" s="30"/>
+      <c r="N107" s="27"/>
     </row>
     <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N108" s="30"/>
+      <c r="N108" s="27"/>
     </row>
     <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N109" s="30"/>
+      <c r="N109" s="27"/>
     </row>
     <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N110" s="30"/>
+      <c r="N110" s="27"/>
     </row>
     <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N111" s="30"/>
+      <c r="N111" s="27"/>
     </row>
     <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N112" s="30"/>
+      <c r="N112" s="27"/>
     </row>
     <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N113" s="30"/>
+      <c r="N113" s="27"/>
     </row>
     <row r="114" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N114" s="30"/>
+      <c r="N114" s="27"/>
     </row>
     <row r="115" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N115" s="30"/>
+      <c r="N115" s="27"/>
     </row>
     <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N116" s="30"/>
+      <c r="N116" s="27"/>
     </row>
     <row r="117" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N117" s="30"/>
+      <c r="N117" s="27"/>
     </row>
     <row r="118" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N118" s="30"/>
+      <c r="N118" s="27"/>
     </row>
     <row r="119" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N119" s="30"/>
+      <c r="N119" s="27"/>
     </row>
     <row r="120" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N120" s="30"/>
+      <c r="N120" s="27"/>
     </row>
     <row r="121" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N121" s="30"/>
+      <c r="N121" s="27"/>
     </row>
     <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N122" s="30"/>
+      <c r="N122" s="27"/>
     </row>
     <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N123" s="30"/>
+      <c r="N123" s="27"/>
     </row>
     <row r="124" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N124" s="30"/>
+      <c r="N124" s="27"/>
     </row>
     <row r="125" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N125" s="30"/>
+      <c r="N125" s="27"/>
     </row>
     <row r="126" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N126" s="30"/>
+      <c r="N126" s="27"/>
     </row>
     <row r="127" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N127" s="30"/>
+      <c r="N127" s="27"/>
     </row>
     <row r="128" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N128" s="30"/>
+      <c r="N128" s="27"/>
     </row>
     <row r="129" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N129" s="30"/>
+      <c r="N129" s="27"/>
     </row>
     <row r="130" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N130" s="30"/>
+      <c r="N130" s="27"/>
     </row>
     <row r="131" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N131" s="30"/>
+      <c r="N131" s="27"/>
     </row>
     <row r="132" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N132" s="30"/>
+      <c r="N132" s="27"/>
     </row>
     <row r="133" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N133" s="30"/>
+      <c r="N133" s="27"/>
     </row>
     <row r="134" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N134" s="30"/>
+      <c r="N134" s="27"/>
     </row>
     <row r="135" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N135" s="30"/>
+      <c r="N135" s="27"/>
     </row>
     <row r="136" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N136" s="30"/>
+      <c r="N136" s="27"/>
     </row>
     <row r="137" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N137" s="30"/>
+      <c r="N137" s="27"/>
     </row>
     <row r="138" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N138" s="30"/>
+      <c r="N138" s="27"/>
     </row>
     <row r="139" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N139" s="30"/>
+      <c r="N139" s="27"/>
     </row>
     <row r="140" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N140" s="30"/>
+      <c r="N140" s="27"/>
     </row>
     <row r="141" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N141" s="30"/>
+      <c r="N141" s="27"/>
     </row>
     <row r="142" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N142" s="30"/>
+      <c r="N142" s="27"/>
     </row>
     <row r="143" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N143" s="30"/>
+      <c r="N143" s="27"/>
     </row>
     <row r="144" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N144" s="30"/>
+      <c r="N144" s="27"/>
     </row>
     <row r="145" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N145" s="30"/>
+      <c r="N145" s="27"/>
     </row>
     <row r="146" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N146" s="30"/>
+      <c r="N146" s="27"/>
     </row>
     <row r="147" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N147" s="30"/>
+      <c r="N147" s="27"/>
     </row>
     <row r="148" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N148" s="30"/>
+      <c r="N148" s="27"/>
     </row>
     <row r="149" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N149" s="30"/>
+      <c r="N149" s="27"/>
     </row>
     <row r="150" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N150" s="30"/>
+      <c r="N150" s="27"/>
     </row>
     <row r="151" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N151" s="30"/>
+      <c r="N151" s="27"/>
     </row>
     <row r="152" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N152" s="30"/>
+      <c r="N152" s="27"/>
     </row>
     <row r="153" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N153" s="30"/>
+      <c r="N153" s="27"/>
     </row>
     <row r="154" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N154" s="30"/>
+      <c r="N154" s="27"/>
     </row>
     <row r="155" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N155" s="30"/>
+      <c r="N155" s="27"/>
     </row>
     <row r="156" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N156" s="30"/>
+      <c r="N156" s="27"/>
     </row>
     <row r="157" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N157" s="30"/>
+      <c r="N157" s="27"/>
     </row>
     <row r="158" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N158" s="30"/>
+      <c r="N158" s="27"/>
     </row>
     <row r="159" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N159" s="30"/>
+      <c r="N159" s="27"/>
     </row>
     <row r="160" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N160" s="30"/>
+      <c r="N160" s="27"/>
     </row>
     <row r="161" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N161" s="30"/>
+      <c r="N161" s="27"/>
     </row>
     <row r="162" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N162" s="30"/>
+      <c r="N162" s="27"/>
     </row>
     <row r="163" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N163" s="30"/>
+      <c r="N163" s="27"/>
     </row>
     <row r="164" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N164" s="30"/>
+      <c r="N164" s="27"/>
     </row>
     <row r="165" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N165" s="30"/>
+      <c r="N165" s="27"/>
     </row>
     <row r="166" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N166" s="30"/>
+      <c r="N166" s="27"/>
     </row>
     <row r="167" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N167" s="30"/>
+      <c r="N167" s="27"/>
     </row>
     <row r="168" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N168" s="30"/>
+      <c r="N168" s="27"/>
     </row>
     <row r="169" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N169" s="30"/>
+      <c r="N169" s="27"/>
     </row>
     <row r="170" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N170" s="30"/>
+      <c r="N170" s="27"/>
     </row>
     <row r="171" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N171" s="30"/>
+      <c r="N171" s="27"/>
     </row>
     <row r="172" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N172" s="30"/>
+      <c r="N172" s="27"/>
     </row>
     <row r="173" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N173" s="30"/>
+      <c r="N173" s="27"/>
     </row>
     <row r="174" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N174" s="30"/>
+      <c r="N174" s="27"/>
     </row>
     <row r="175" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N175" s="30"/>
+      <c r="N175" s="27"/>
     </row>
     <row r="176" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N176" s="30"/>
+      <c r="N176" s="27"/>
     </row>
     <row r="177" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N177" s="30"/>
+      <c r="N177" s="27"/>
     </row>
     <row r="178" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N178" s="30"/>
+      <c r="N178" s="27"/>
     </row>
     <row r="179" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N179" s="30"/>
+      <c r="N179" s="27"/>
     </row>
     <row r="180" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N180" s="30"/>
+      <c r="N180" s="27"/>
     </row>
     <row r="181" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N181" s="30"/>
+      <c r="N181" s="27"/>
     </row>
     <row r="182" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N182" s="30"/>
+      <c r="N182" s="27"/>
     </row>
     <row r="183" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N183" s="30"/>
+      <c r="N183" s="27"/>
     </row>
     <row r="184" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N184" s="30"/>
+      <c r="N184" s="27"/>
     </row>
     <row r="185" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N185" s="30"/>
+      <c r="N185" s="27"/>
     </row>
     <row r="186" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N186" s="30"/>
+      <c r="N186" s="27"/>
     </row>
     <row r="187" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N187" s="30"/>
+      <c r="N187" s="27"/>
     </row>
     <row r="188" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N188" s="30"/>
+      <c r="N188" s="27"/>
     </row>
     <row r="189" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N189" s="30"/>
+      <c r="N189" s="27"/>
     </row>
     <row r="190" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N190" s="30"/>
+      <c r="N190" s="27"/>
     </row>
     <row r="191" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N191" s="30"/>
+      <c r="N191" s="27"/>
     </row>
     <row r="192" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N192" s="30"/>
+      <c r="N192" s="27"/>
     </row>
     <row r="193" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N193" s="30"/>
+      <c r="N193" s="27"/>
     </row>
     <row r="194" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N194" s="30"/>
+      <c r="N194" s="27"/>
     </row>
     <row r="195" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N195" s="30"/>
+      <c r="N195" s="27"/>
     </row>
     <row r="196" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N196" s="30"/>
+      <c r="N196" s="27"/>
     </row>
     <row r="197" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N197" s="30"/>
+      <c r="N197" s="27"/>
     </row>
     <row r="198" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N198" s="30"/>
+      <c r="N198" s="27"/>
     </row>
     <row r="199" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N199" s="30"/>
+      <c r="N199" s="27"/>
     </row>
     <row r="200" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N200" s="30"/>
+      <c r="N200" s="27"/>
     </row>
     <row r="201" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N201" s="30"/>
+      <c r="N201" s="27"/>
     </row>
     <row r="202" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N202" s="30"/>
+      <c r="N202" s="27"/>
     </row>
     <row r="203" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N203" s="30"/>
+      <c r="N203" s="27"/>
     </row>
     <row r="204" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N204" s="30"/>
+      <c r="N204" s="27"/>
     </row>
     <row r="205" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N205" s="30"/>
+      <c r="N205" s="27"/>
     </row>
     <row r="206" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N206" s="30"/>
+      <c r="N206" s="27"/>
     </row>
     <row r="207" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N207" s="30"/>
+      <c r="N207" s="27"/>
     </row>
     <row r="208" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N208" s="30"/>
+      <c r="N208" s="27"/>
     </row>
     <row r="209" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N209" s="30"/>
+      <c r="N209" s="27"/>
     </row>
     <row r="210" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N210" s="30"/>
+      <c r="N210" s="27"/>
     </row>
     <row r="211" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N211" s="30"/>
+      <c r="N211" s="27"/>
     </row>
     <row r="212" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N212" s="30"/>
+      <c r="N212" s="27"/>
     </row>
     <row r="213" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N213" s="30"/>
+      <c r="N213" s="27"/>
     </row>
     <row r="214" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N214" s="30"/>
+      <c r="N214" s="27"/>
     </row>
     <row r="215" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N215" s="30"/>
+      <c r="N215" s="27"/>
     </row>
     <row r="216" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N216" s="30"/>
+      <c r="N216" s="27"/>
     </row>
     <row r="217" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N217" s="30"/>
+      <c r="N217" s="27"/>
     </row>
     <row r="218" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N218" s="30"/>
+      <c r="N218" s="27"/>
     </row>
     <row r="219" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N219" s="30"/>
+      <c r="N219" s="27"/>
     </row>
     <row r="220" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N220" s="30"/>
+      <c r="N220" s="27"/>
     </row>
     <row r="221" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N221" s="30"/>
+      <c r="N221" s="27"/>
     </row>
     <row r="222" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N222" s="30"/>
+      <c r="N222" s="27"/>
     </row>
     <row r="223" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N223" s="30"/>
+      <c r="N223" s="27"/>
     </row>
     <row r="224" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N224" s="30"/>
+      <c r="N224" s="27"/>
     </row>
     <row r="225" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N225" s="30"/>
+      <c r="N225" s="27"/>
     </row>
     <row r="226" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N226" s="30"/>
+      <c r="N226" s="27"/>
     </row>
     <row r="227" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N227" s="30"/>
+      <c r="N227" s="27"/>
     </row>
     <row r="228" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N228" s="30"/>
+      <c r="N228" s="27"/>
     </row>
     <row r="229" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N229" s="30"/>
+      <c r="N229" s="27"/>
     </row>
     <row r="230" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N230" s="30"/>
+      <c r="N230" s="27"/>
     </row>
     <row r="231" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N231" s="30"/>
+      <c r="N231" s="27"/>
     </row>
     <row r="232" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N232" s="30"/>
+      <c r="N232" s="27"/>
     </row>
     <row r="233" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N233" s="30"/>
+      <c r="N233" s="27"/>
     </row>
     <row r="234" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N234" s="30"/>
+      <c r="N234" s="27"/>
     </row>
     <row r="235" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N235" s="30"/>
+      <c r="N235" s="27"/>
     </row>
     <row r="236" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N236" s="30"/>
+      <c r="N236" s="27"/>
     </row>
     <row r="237" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N237" s="30"/>
+      <c r="N237" s="27"/>
     </row>
     <row r="238" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N238" s="30"/>
+      <c r="N238" s="27"/>
     </row>
     <row r="239" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N239" s="30"/>
+      <c r="N239" s="27"/>
     </row>
     <row r="240" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N240" s="30"/>
+      <c r="N240" s="27"/>
     </row>
     <row r="241" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N241" s="30"/>
+      <c r="N241" s="27"/>
     </row>
     <row r="242" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N242" s="30"/>
+      <c r="N242" s="27"/>
     </row>
     <row r="243" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N243" s="30"/>
+      <c r="N243" s="27"/>
     </row>
     <row r="244" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N244" s="30"/>
+      <c r="N244" s="27"/>
     </row>
     <row r="245" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N245" s="30"/>
+      <c r="N245" s="27"/>
     </row>
     <row r="246" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N246" s="30"/>
+      <c r="N246" s="27"/>
     </row>
     <row r="247" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N247" s="30"/>
+      <c r="N247" s="27"/>
     </row>
     <row r="248" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N248" s="30"/>
+      <c r="N248" s="27"/>
     </row>
     <row r="249" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N249" s="30"/>
+      <c r="N249" s="27"/>
     </row>
     <row r="250" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N250" s="30"/>
+      <c r="N250" s="27"/>
     </row>
     <row r="251" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N251" s="30"/>
+      <c r="N251" s="27"/>
     </row>
     <row r="252" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N252" s="30"/>
+      <c r="N252" s="27"/>
     </row>
     <row r="253" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N253" s="30"/>
+      <c r="N253" s="27"/>
     </row>
     <row r="254" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N254" s="30"/>
+      <c r="N254" s="27"/>
     </row>
     <row r="255" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N255" s="30"/>
+      <c r="N255" s="27"/>
     </row>
     <row r="256" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N256" s="30"/>
+      <c r="N256" s="27"/>
     </row>
     <row r="257" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N257" s="30"/>
+      <c r="N257" s="27"/>
     </row>
     <row r="258" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N258" s="30"/>
+      <c r="N258" s="27"/>
     </row>
     <row r="259" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N259" s="30"/>
+      <c r="N259" s="27"/>
     </row>
     <row r="260" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N260" s="30"/>
+      <c r="N260" s="27"/>
     </row>
     <row r="261" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N261" s="30"/>
+      <c r="N261" s="27"/>
     </row>
     <row r="262" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N262" s="30"/>
+      <c r="N262" s="27"/>
     </row>
     <row r="263" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N263" s="30"/>
+      <c r="N263" s="27"/>
     </row>
     <row r="264" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N264" s="30"/>
+      <c r="N264" s="27"/>
     </row>
     <row r="265" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N265" s="30"/>
+      <c r="N265" s="27"/>
     </row>
     <row r="266" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N266" s="30"/>
+      <c r="N266" s="27"/>
     </row>
     <row r="267" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N267" s="30"/>
+      <c r="N267" s="27"/>
     </row>
     <row r="268" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N268" s="30"/>
+      <c r="N268" s="27"/>
     </row>
     <row r="269" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N269" s="30"/>
+      <c r="N269" s="27"/>
     </row>
     <row r="270" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N270" s="30"/>
+      <c r="N270" s="27"/>
     </row>
     <row r="271" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N271" s="30"/>
+      <c r="N271" s="27"/>
     </row>
     <row r="272" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N272" s="30"/>
+      <c r="N272" s="27"/>
     </row>
     <row r="273" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N273" s="30"/>
+      <c r="N273" s="27"/>
     </row>
     <row r="274" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N274" s="30"/>
+      <c r="N274" s="27"/>
     </row>
     <row r="275" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N275" s="30"/>
+      <c r="N275" s="27"/>
     </row>
     <row r="276" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N276" s="30"/>
+      <c r="N276" s="27"/>
     </row>
     <row r="277" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N277" s="30"/>
+      <c r="N277" s="27"/>
     </row>
     <row r="278" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N278" s="30"/>
+      <c r="N278" s="27"/>
     </row>
     <row r="279" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N279" s="30"/>
+      <c r="N279" s="27"/>
     </row>
     <row r="280" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N280" s="30"/>
+      <c r="N280" s="27"/>
     </row>
     <row r="281" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N281" s="30"/>
+      <c r="N281" s="27"/>
     </row>
     <row r="282" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N282" s="30"/>
+      <c r="N282" s="27"/>
     </row>
     <row r="283" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N283" s="30"/>
+      <c r="N283" s="27"/>
     </row>
     <row r="284" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N284" s="30"/>
+      <c r="N284" s="27"/>
     </row>
     <row r="285" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N285" s="30"/>
+      <c r="N285" s="27"/>
     </row>
     <row r="286" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N286" s="30"/>
+      <c r="N286" s="27"/>
     </row>
     <row r="287" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N287" s="30"/>
+      <c r="N287" s="27"/>
     </row>
     <row r="288" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N288" s="30"/>
+      <c r="N288" s="27"/>
     </row>
     <row r="289" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N289" s="30"/>
+      <c r="N289" s="27"/>
     </row>
     <row r="290" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N290" s="30"/>
+      <c r="N290" s="27"/>
     </row>
     <row r="291" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N291" s="30"/>
+      <c r="N291" s="27"/>
     </row>
     <row r="292" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N292" s="30"/>
+      <c r="N292" s="27"/>
     </row>
     <row r="293" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N293" s="30"/>
+      <c r="N293" s="27"/>
     </row>
     <row r="294" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N294" s="30"/>
+      <c r="N294" s="27"/>
     </row>
     <row r="295" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N295" s="30"/>
+      <c r="N295" s="27"/>
     </row>
     <row r="296" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N296" s="30"/>
+      <c r="N296" s="27"/>
     </row>
     <row r="297" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N297" s="30"/>
+      <c r="N297" s="27"/>
     </row>
     <row r="298" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N298" s="30"/>
+      <c r="N298" s="27"/>
     </row>
     <row r="299" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N299" s="30"/>
+      <c r="N299" s="27"/>
     </row>
     <row r="300" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N300" s="30"/>
+      <c r="N300" s="27"/>
     </row>
     <row r="301" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N301" s="30"/>
+      <c r="N301" s="27"/>
     </row>
     <row r="302" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N302" s="30"/>
+      <c r="N302" s="27"/>
     </row>
     <row r="303" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N303" s="30"/>
+      <c r="N303" s="27"/>
     </row>
     <row r="304" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N304" s="30"/>
+      <c r="N304" s="27"/>
     </row>
     <row r="305" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N305" s="30"/>
+      <c r="N305" s="27"/>
     </row>
     <row r="306" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N306" s="30"/>
+      <c r="N306" s="27"/>
     </row>
     <row r="307" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N307" s="30"/>
+      <c r="N307" s="27"/>
     </row>
     <row r="308" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N308" s="30"/>
+      <c r="N308" s="27"/>
     </row>
     <row r="309" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N309" s="30"/>
+      <c r="N309" s="27"/>
     </row>
     <row r="310" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N310" s="30"/>
+      <c r="N310" s="27"/>
     </row>
     <row r="311" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N311" s="30"/>
+      <c r="N311" s="27"/>
     </row>
     <row r="312" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N312" s="30"/>
+      <c r="N312" s="27"/>
     </row>
     <row r="313" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N313" s="30"/>
+      <c r="N313" s="27"/>
     </row>
     <row r="314" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N314" s="30"/>
+      <c r="N314" s="27"/>
     </row>
     <row r="315" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N315" s="30"/>
+      <c r="N315" s="27"/>
     </row>
     <row r="316" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N316" s="30"/>
+      <c r="N316" s="27"/>
     </row>
     <row r="317" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N317" s="30"/>
+      <c r="N317" s="27"/>
     </row>
     <row r="318" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N318" s="30"/>
+      <c r="N318" s="27"/>
     </row>
     <row r="319" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N319" s="30"/>
+      <c r="N319" s="27"/>
     </row>
     <row r="320" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N320" s="30"/>
+      <c r="N320" s="27"/>
     </row>
     <row r="321" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N321" s="30"/>
+      <c r="N321" s="27"/>
     </row>
     <row r="322" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N322" s="30"/>
+      <c r="N322" s="27"/>
     </row>
     <row r="323" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N323" s="30"/>
+      <c r="N323" s="27"/>
     </row>
     <row r="324" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N324" s="30"/>
+      <c r="N324" s="27"/>
     </row>
     <row r="325" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N325" s="30"/>
+      <c r="N325" s="27"/>
     </row>
     <row r="326" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N326" s="30"/>
+      <c r="N326" s="27"/>
     </row>
     <row r="327" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N327" s="30"/>
+      <c r="N327" s="27"/>
     </row>
     <row r="328" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N328" s="30"/>
+      <c r="N328" s="27"/>
     </row>
     <row r="329" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N329" s="30"/>
+      <c r="N329" s="27"/>
     </row>
     <row r="330" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N330" s="30"/>
+      <c r="N330" s="27"/>
     </row>
     <row r="331" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N331" s="30"/>
+      <c r="N331" s="27"/>
     </row>
     <row r="332" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N332" s="30"/>
+      <c r="N332" s="27"/>
     </row>
     <row r="333" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N333" s="30"/>
+      <c r="N333" s="27"/>
     </row>
     <row r="334" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N334" s="30"/>
+      <c r="N334" s="27"/>
     </row>
     <row r="335" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N335" s="30"/>
+      <c r="N335" s="27"/>
     </row>
     <row r="336" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N336" s="30"/>
+      <c r="N336" s="27"/>
     </row>
     <row r="337" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N337" s="30"/>
+      <c r="N337" s="27"/>
     </row>
     <row r="338" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N338" s="30"/>
+      <c r="N338" s="27"/>
     </row>
     <row r="339" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N339" s="30"/>
+      <c r="N339" s="27"/>
     </row>
     <row r="340" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N340" s="30"/>
+      <c r="N340" s="27"/>
     </row>
     <row r="341" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N341" s="30"/>
+      <c r="N341" s="27"/>
     </row>
     <row r="342" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N342" s="30"/>
+      <c r="N342" s="27"/>
     </row>
     <row r="343" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N343" s="30"/>
+      <c r="N343" s="27"/>
     </row>
     <row r="344" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N344" s="30"/>
+      <c r="N344" s="27"/>
     </row>
     <row r="345" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N345" s="30"/>
+      <c r="N345" s="27"/>
     </row>
     <row r="346" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N346" s="30"/>
+      <c r="N346" s="27"/>
     </row>
     <row r="347" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N347" s="30"/>
+      <c r="N347" s="27"/>
     </row>
     <row r="348" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N348" s="30"/>
+      <c r="N348" s="27"/>
     </row>
     <row r="349" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N349" s="30"/>
+      <c r="N349" s="27"/>
     </row>
     <row r="350" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N350" s="30"/>
+      <c r="N350" s="27"/>
     </row>
     <row r="351" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N351" s="30"/>
+      <c r="N351" s="27"/>
     </row>
     <row r="352" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N352" s="30"/>
+      <c r="N352" s="27"/>
     </row>
     <row r="353" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N353" s="30"/>
+      <c r="N353" s="27"/>
     </row>
     <row r="354" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N354" s="30"/>
+      <c r="N354" s="27"/>
     </row>
     <row r="355" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N355" s="30"/>
+      <c r="N355" s="27"/>
     </row>
     <row r="356" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N356" s="30"/>
+      <c r="N356" s="27"/>
     </row>
     <row r="357" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N357" s="30"/>
+      <c r="N357" s="27"/>
     </row>
     <row r="358" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N358" s="30"/>
+      <c r="N358" s="27"/>
     </row>
     <row r="359" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N359" s="30"/>
+      <c r="N359" s="27"/>
     </row>
     <row r="360" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N360" s="30"/>
+      <c r="N360" s="27"/>
     </row>
     <row r="361" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N361" s="30"/>
+      <c r="N361" s="27"/>
     </row>
     <row r="362" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N362" s="30"/>
+      <c r="N362" s="27"/>
     </row>
     <row r="363" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N363" s="30"/>
+      <c r="N363" s="27"/>
     </row>
     <row r="364" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N364" s="30"/>
+      <c r="N364" s="27"/>
     </row>
     <row r="365" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N365" s="30"/>
+      <c r="N365" s="27"/>
     </row>
     <row r="366" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N366" s="30"/>
+      <c r="N366" s="27"/>
     </row>
     <row r="367" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N367" s="30"/>
+      <c r="N367" s="27"/>
     </row>
     <row r="368" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N368" s="30"/>
+      <c r="N368" s="27"/>
     </row>
     <row r="369" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N369" s="30"/>
+      <c r="N369" s="27"/>
     </row>
     <row r="370" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N370" s="30"/>
+      <c r="N370" s="27"/>
     </row>
     <row r="371" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N371" s="30"/>
+      <c r="N371" s="27"/>
     </row>
     <row r="372" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N372" s="30"/>
+      <c r="N372" s="27"/>
     </row>
     <row r="373" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N373" s="30"/>
+      <c r="N373" s="27"/>
     </row>
     <row r="374" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N374" s="30"/>
+      <c r="N374" s="27"/>
     </row>
     <row r="375" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N375" s="30"/>
+      <c r="N375" s="27"/>
     </row>
     <row r="376" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N376" s="30"/>
+      <c r="N376" s="27"/>
     </row>
     <row r="377" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N377" s="30"/>
+      <c r="N377" s="27"/>
     </row>
     <row r="378" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N378" s="30"/>
+      <c r="N378" s="27"/>
     </row>
     <row r="379" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N379" s="30"/>
+      <c r="N379" s="27"/>
     </row>
     <row r="380" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N380" s="30"/>
+      <c r="N380" s="27"/>
     </row>
     <row r="381" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N381" s="30"/>
+      <c r="N381" s="27"/>
     </row>
     <row r="382" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N382" s="30"/>
+      <c r="N382" s="27"/>
     </row>
     <row r="383" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N383" s="30"/>
+      <c r="N383" s="27"/>
     </row>
     <row r="384" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N384" s="30"/>
+      <c r="N384" s="27"/>
     </row>
     <row r="385" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N385" s="30"/>
+      <c r="N385" s="27"/>
     </row>
     <row r="386" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N386" s="30"/>
+      <c r="N386" s="27"/>
     </row>
     <row r="387" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N387" s="30"/>
+      <c r="N387" s="27"/>
     </row>
     <row r="388" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N388" s="30"/>
+      <c r="N388" s="27"/>
     </row>
     <row r="389" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N389" s="30"/>
+      <c r="N389" s="27"/>
     </row>
     <row r="390" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N390" s="30"/>
+      <c r="N390" s="27"/>
     </row>
     <row r="391" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N391" s="30"/>
+      <c r="N391" s="27"/>
     </row>
     <row r="392" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N392" s="30"/>
+      <c r="N392" s="27"/>
     </row>
     <row r="393" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N393" s="30"/>
+      <c r="N393" s="27"/>
     </row>
     <row r="394" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N394" s="30"/>
+      <c r="N394" s="27"/>
     </row>
     <row r="395" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N395" s="30"/>
+      <c r="N395" s="27"/>
     </row>
     <row r="396" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N396" s="30"/>
+      <c r="N396" s="27"/>
     </row>
     <row r="397" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N397" s="30"/>
+      <c r="N397" s="27"/>
     </row>
     <row r="398" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N398" s="30"/>
+      <c r="N398" s="27"/>
     </row>
     <row r="399" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N399" s="30"/>
+      <c r="N399" s="27"/>
     </row>
     <row r="400" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N400" s="30"/>
+      <c r="N400" s="27"/>
     </row>
     <row r="401" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N401" s="30"/>
+      <c r="N401" s="27"/>
     </row>
     <row r="402" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N402" s="30"/>
+      <c r="N402" s="27"/>
     </row>
     <row r="403" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N403" s="30"/>
+      <c r="N403" s="27"/>
     </row>
     <row r="404" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N404" s="30"/>
+      <c r="N404" s="27"/>
     </row>
     <row r="405" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N405" s="30"/>
+      <c r="N405" s="27"/>
     </row>
     <row r="406" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N406" s="30"/>
+      <c r="N406" s="27"/>
     </row>
     <row r="407" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N407" s="30"/>
+      <c r="N407" s="27"/>
     </row>
     <row r="408" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N408" s="30"/>
+      <c r="N408" s="27"/>
     </row>
     <row r="409" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N409" s="30"/>
+      <c r="N409" s="27"/>
     </row>
     <row r="410" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N410" s="30"/>
+      <c r="N410" s="27"/>
     </row>
     <row r="411" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N411" s="30"/>
+      <c r="N411" s="27"/>
     </row>
     <row r="412" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N412" s="30"/>
+      <c r="N412" s="27"/>
     </row>
     <row r="413" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N413" s="30"/>
+      <c r="N413" s="27"/>
     </row>
     <row r="414" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N414" s="30"/>
+      <c r="N414" s="27"/>
     </row>
     <row r="415" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N415" s="30"/>
+      <c r="N415" s="27"/>
     </row>
     <row r="416" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N416" s="30"/>
+      <c r="N416" s="27"/>
     </row>
     <row r="417" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N417" s="30"/>
+      <c r="N417" s="27"/>
     </row>
     <row r="418" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N418" s="30"/>
+      <c r="N418" s="27"/>
     </row>
     <row r="419" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N419" s="30"/>
+      <c r="N419" s="27"/>
     </row>
     <row r="420" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N420" s="30"/>
+      <c r="N420" s="27"/>
     </row>
     <row r="421" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N421" s="30"/>
+      <c r="N421" s="27"/>
     </row>
     <row r="422" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N422" s="30"/>
+      <c r="N422" s="27"/>
     </row>
     <row r="423" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N423" s="30"/>
+      <c r="N423" s="27"/>
     </row>
     <row r="424" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N424" s="30"/>
+      <c r="N424" s="27"/>
     </row>
     <row r="425" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N425" s="30"/>
+      <c r="N425" s="27"/>
     </row>
     <row r="426" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N426" s="30"/>
+      <c r="N426" s="27"/>
     </row>
     <row r="427" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N427" s="30"/>
+      <c r="N427" s="27"/>
     </row>
     <row r="428" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N428" s="30"/>
+      <c r="N428" s="27"/>
     </row>
     <row r="429" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N429" s="30"/>
+      <c r="N429" s="27"/>
     </row>
     <row r="430" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N430" s="30"/>
+      <c r="N430" s="27"/>
     </row>
     <row r="431" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N431" s="30"/>
+      <c r="N431" s="27"/>
     </row>
     <row r="432" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N432" s="30"/>
+      <c r="N432" s="27"/>
     </row>
     <row r="433" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N433" s="30"/>
+      <c r="N433" s="27"/>
     </row>
     <row r="434" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N434" s="30"/>
+      <c r="N434" s="27"/>
     </row>
     <row r="435" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N435" s="30"/>
+      <c r="N435" s="27"/>
     </row>
     <row r="436" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N436" s="30"/>
+      <c r="N436" s="27"/>
     </row>
     <row r="437" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N437" s="30"/>
+      <c r="N437" s="27"/>
     </row>
     <row r="438" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N438" s="30"/>
+      <c r="N438" s="27"/>
     </row>
     <row r="439" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N439" s="30"/>
+      <c r="N439" s="27"/>
     </row>
     <row r="440" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N440" s="30"/>
+      <c r="N440" s="27"/>
     </row>
     <row r="441" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N441" s="30"/>
+      <c r="N441" s="27"/>
     </row>
     <row r="442" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N442" s="30"/>
+      <c r="N442" s="27"/>
     </row>
     <row r="443" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N443" s="30"/>
+      <c r="N443" s="27"/>
     </row>
     <row r="444" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N444" s="30"/>
+      <c r="N444" s="27"/>
     </row>
     <row r="445" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N445" s="30"/>
+      <c r="N445" s="27"/>
     </row>
     <row r="446" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N446" s="30"/>
+      <c r="N446" s="27"/>
     </row>
     <row r="447" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N447" s="30"/>
+      <c r="N447" s="27"/>
     </row>
     <row r="448" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N448" s="30"/>
+      <c r="N448" s="27"/>
     </row>
     <row r="449" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N449" s="30"/>
+      <c r="N449" s="27"/>
     </row>
     <row r="450" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N450" s="30"/>
+      <c r="N450" s="27"/>
     </row>
     <row r="451" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N451" s="30"/>
+      <c r="N451" s="27"/>
     </row>
     <row r="452" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N452" s="30"/>
+      <c r="N452" s="27"/>
     </row>
     <row r="453" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N453" s="30"/>
+      <c r="N453" s="27"/>
     </row>
     <row r="454" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N454" s="30"/>
+      <c r="N454" s="27"/>
     </row>
     <row r="455" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N455" s="30"/>
+      <c r="N455" s="27"/>
     </row>
     <row r="456" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N456" s="30"/>
+      <c r="N456" s="27"/>
     </row>
     <row r="457" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N457" s="30"/>
+      <c r="N457" s="27"/>
     </row>
     <row r="458" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N458" s="30"/>
+      <c r="N458" s="27"/>
     </row>
     <row r="459" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N459" s="30"/>
+      <c r="N459" s="27"/>
     </row>
     <row r="460" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N460" s="30"/>
+      <c r="N460" s="27"/>
     </row>
     <row r="461" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N461" s="30"/>
+      <c r="N461" s="27"/>
     </row>
     <row r="462" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N462" s="30"/>
+      <c r="N462" s="27"/>
     </row>
     <row r="463" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N463" s="30"/>
+      <c r="N463" s="27"/>
     </row>
     <row r="464" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N464" s="30"/>
+      <c r="N464" s="27"/>
     </row>
     <row r="465" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N465" s="30"/>
+      <c r="N465" s="27"/>
     </row>
     <row r="466" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N466" s="30"/>
+      <c r="N466" s="27"/>
     </row>
     <row r="467" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N467" s="30"/>
+      <c r="N467" s="27"/>
     </row>
     <row r="468" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N468" s="30"/>
+      <c r="N468" s="27"/>
     </row>
     <row r="469" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N469" s="30"/>
+      <c r="N469" s="27"/>
     </row>
     <row r="470" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N470" s="30"/>
+      <c r="N470" s="27"/>
     </row>
     <row r="471" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N471" s="30"/>
+      <c r="N471" s="27"/>
     </row>
     <row r="472" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N472" s="30"/>
+      <c r="N472" s="27"/>
     </row>
     <row r="473" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N473" s="30"/>
+      <c r="N473" s="27"/>
     </row>
     <row r="474" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N474" s="30"/>
+      <c r="N474" s="27"/>
     </row>
     <row r="475" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N475" s="30"/>
+      <c r="N475" s="27"/>
     </row>
     <row r="476" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N476" s="30"/>
+      <c r="N476" s="27"/>
     </row>
     <row r="477" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N477" s="30"/>
+      <c r="N477" s="27"/>
     </row>
     <row r="478" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N478" s="30"/>
+      <c r="N478" s="27"/>
     </row>
     <row r="479" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N479" s="30"/>
+      <c r="N479" s="27"/>
     </row>
     <row r="480" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N480" s="30"/>
+      <c r="N480" s="27"/>
     </row>
     <row r="481" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N481" s="30"/>
+      <c r="N481" s="27"/>
     </row>
     <row r="482" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N482" s="30"/>
+      <c r="N482" s="27"/>
     </row>
     <row r="483" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N483" s="30"/>
+      <c r="N483" s="27"/>
     </row>
     <row r="484" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N484" s="30"/>
+      <c r="N484" s="27"/>
     </row>
     <row r="485" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N485" s="30"/>
+      <c r="N485" s="27"/>
     </row>
     <row r="486" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N486" s="30"/>
+      <c r="N486" s="27"/>
     </row>
     <row r="487" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N487" s="30"/>
+      <c r="N487" s="27"/>
     </row>
     <row r="488" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N488" s="30"/>
+      <c r="N488" s="27"/>
     </row>
     <row r="489" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N489" s="30"/>
+      <c r="N489" s="27"/>
     </row>
     <row r="490" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N490" s="30"/>
+      <c r="N490" s="27"/>
     </row>
     <row r="491" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N491" s="30"/>
+      <c r="N491" s="27"/>
     </row>
     <row r="492" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N492" s="30"/>
+      <c r="N492" s="27"/>
     </row>
     <row r="493" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N493" s="30"/>
+      <c r="N493" s="27"/>
     </row>
     <row r="494" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N494" s="30"/>
+      <c r="N494" s="27"/>
     </row>
     <row r="495" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N495" s="30"/>
+      <c r="N495" s="27"/>
     </row>
     <row r="496" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N496" s="30"/>
+      <c r="N496" s="27"/>
     </row>
     <row r="497" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N497" s="30"/>
+      <c r="N497" s="27"/>
     </row>
     <row r="498" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N498" s="30"/>
+      <c r="N498" s="27"/>
     </row>
     <row r="499" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N499" s="30"/>
+      <c r="N499" s="27"/>
     </row>
     <row r="500" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N500" s="30"/>
+      <c r="N500" s="27"/>
     </row>
     <row r="501" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N501" s="30"/>
+      <c r="N501" s="27"/>
     </row>
     <row r="502" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N502" s="30"/>
+      <c r="N502" s="27"/>
     </row>
     <row r="503" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N503" s="30"/>
+      <c r="N503" s="27"/>
     </row>
     <row r="504" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N504" s="30"/>
+      <c r="N504" s="27"/>
     </row>
     <row r="505" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N505" s="30"/>
+      <c r="N505" s="27"/>
     </row>
     <row r="506" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N506" s="30"/>
+      <c r="N506" s="27"/>
     </row>
     <row r="507" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N507" s="30"/>
+      <c r="N507" s="27"/>
     </row>
     <row r="508" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N508" s="30"/>
+      <c r="N508" s="27"/>
     </row>
     <row r="509" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N509" s="30"/>
+      <c r="N509" s="27"/>
     </row>
     <row r="510" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N510" s="30"/>
+      <c r="N510" s="27"/>
     </row>
     <row r="511" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N511" s="30"/>
+      <c r="N511" s="27"/>
     </row>
     <row r="512" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N512" s="30"/>
+      <c r="N512" s="27"/>
     </row>
     <row r="513" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N513" s="30"/>
+      <c r="N513" s="27"/>
     </row>
     <row r="514" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N514" s="30"/>
+      <c r="N514" s="27"/>
     </row>
     <row r="515" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N515" s="30"/>
+      <c r="N515" s="27"/>
     </row>
     <row r="516" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N516" s="30"/>
+      <c r="N516" s="27"/>
     </row>
     <row r="517" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N517" s="30"/>
+      <c r="N517" s="27"/>
     </row>
     <row r="518" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N518" s="30"/>
+      <c r="N518" s="27"/>
     </row>
     <row r="519" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N519" s="30"/>
+      <c r="N519" s="27"/>
     </row>
     <row r="520" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N520" s="30"/>
+      <c r="N520" s="27"/>
     </row>
     <row r="521" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N521" s="30"/>
+      <c r="N521" s="27"/>
     </row>
     <row r="522" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N522" s="30"/>
+      <c r="N522" s="27"/>
     </row>
     <row r="523" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N523" s="30"/>
+      <c r="N523" s="27"/>
     </row>
     <row r="524" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N524" s="30"/>
+      <c r="N524" s="27"/>
     </row>
     <row r="525" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N525" s="30"/>
+      <c r="N525" s="27"/>
     </row>
     <row r="526" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N526" s="30"/>
+      <c r="N526" s="27"/>
     </row>
     <row r="527" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N527" s="30"/>
+      <c r="N527" s="27"/>
     </row>
     <row r="528" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N528" s="30"/>
+      <c r="N528" s="27"/>
     </row>
     <row r="529" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N529" s="30"/>
+      <c r="N529" s="27"/>
     </row>
     <row r="530" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N530" s="30"/>
+      <c r="N530" s="27"/>
     </row>
     <row r="531" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N531" s="30"/>
+      <c r="N531" s="27"/>
     </row>
     <row r="532" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N532" s="30"/>
+      <c r="N532" s="27"/>
     </row>
     <row r="533" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N533" s="30"/>
+      <c r="N533" s="27"/>
     </row>
     <row r="534" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N534" s="30"/>
+      <c r="N534" s="27"/>
     </row>
     <row r="535" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N535" s="30"/>
+      <c r="N535" s="27"/>
     </row>
     <row r="536" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N536" s="30"/>
+      <c r="N536" s="27"/>
     </row>
     <row r="537" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N537" s="30"/>
+      <c r="N537" s="27"/>
     </row>
     <row r="538" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N538" s="30"/>
+      <c r="N538" s="27"/>
     </row>
     <row r="539" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N539" s="30"/>
+      <c r="N539" s="27"/>
     </row>
     <row r="540" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N540" s="30"/>
+      <c r="N540" s="27"/>
     </row>
     <row r="541" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N541" s="30"/>
+      <c r="N541" s="27"/>
     </row>
     <row r="542" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N542" s="30"/>
+      <c r="N542" s="27"/>
     </row>
     <row r="543" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N543" s="30"/>
+      <c r="N543" s="27"/>
     </row>
     <row r="544" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N544" s="30"/>
+      <c r="N544" s="27"/>
     </row>
     <row r="545" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N545" s="30"/>
+      <c r="N545" s="27"/>
     </row>
     <row r="546" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N546" s="30"/>
+      <c r="N546" s="27"/>
     </row>
     <row r="547" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N547" s="30"/>
+      <c r="N547" s="27"/>
     </row>
     <row r="548" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N548" s="30"/>
+      <c r="N548" s="27"/>
     </row>
     <row r="549" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N549" s="30"/>
+      <c r="N549" s="27"/>
     </row>
     <row r="550" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N550" s="30"/>
+      <c r="N550" s="27"/>
     </row>
     <row r="551" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N551" s="30"/>
+      <c r="N551" s="27"/>
     </row>
     <row r="552" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N552" s="30"/>
+      <c r="N552" s="27"/>
     </row>
     <row r="553" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N553" s="30"/>
+      <c r="N553" s="27"/>
     </row>
     <row r="554" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N554" s="30"/>
+      <c r="N554" s="27"/>
     </row>
     <row r="555" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N555" s="30"/>
+      <c r="N555" s="27"/>
     </row>
     <row r="556" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N556" s="30"/>
+      <c r="N556" s="27"/>
     </row>
     <row r="557" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N557" s="30"/>
+      <c r="N557" s="27"/>
     </row>
     <row r="558" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N558" s="30"/>
+      <c r="N558" s="27"/>
     </row>
     <row r="559" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N559" s="30"/>
+      <c r="N559" s="27"/>
     </row>
     <row r="560" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N560" s="30"/>
+      <c r="N560" s="27"/>
     </row>
     <row r="561" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N561" s="30"/>
+      <c r="N561" s="27"/>
     </row>
     <row r="562" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N562" s="30"/>
+      <c r="N562" s="27"/>
     </row>
     <row r="563" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N563" s="30"/>
+      <c r="N563" s="27"/>
     </row>
     <row r="564" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N564" s="30"/>
+      <c r="N564" s="27"/>
     </row>
     <row r="565" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N565" s="30"/>
+      <c r="N565" s="27"/>
     </row>
     <row r="566" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N566" s="30"/>
+      <c r="N566" s="27"/>
     </row>
     <row r="567" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N567" s="30"/>
+      <c r="N567" s="27"/>
     </row>
     <row r="568" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N568" s="30"/>
+      <c r="N568" s="27"/>
     </row>
     <row r="569" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N569" s="30"/>
+      <c r="N569" s="27"/>
     </row>
     <row r="570" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N570" s="30"/>
+      <c r="N570" s="27"/>
     </row>
     <row r="571" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N571" s="30"/>
+      <c r="N571" s="27"/>
     </row>
     <row r="572" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N572" s="30"/>
+      <c r="N572" s="27"/>
     </row>
     <row r="573" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N573" s="30"/>
+      <c r="N573" s="27"/>
     </row>
     <row r="574" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N574" s="30"/>
+      <c r="N574" s="27"/>
     </row>
     <row r="575" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N575" s="30"/>
+      <c r="N575" s="27"/>
     </row>
     <row r="576" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N576" s="30"/>
+      <c r="N576" s="27"/>
     </row>
     <row r="577" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N577" s="30"/>
+      <c r="N577" s="27"/>
     </row>
     <row r="578" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N578" s="30"/>
+      <c r="N578" s="27"/>
     </row>
     <row r="579" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N579" s="30"/>
+      <c r="N579" s="27"/>
     </row>
     <row r="580" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N580" s="30"/>
+      <c r="N580" s="27"/>
     </row>
     <row r="581" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N581" s="30"/>
+      <c r="N581" s="27"/>
     </row>
     <row r="582" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N582" s="30"/>
+      <c r="N582" s="27"/>
     </row>
     <row r="583" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N583" s="30"/>
+      <c r="N583" s="27"/>
     </row>
     <row r="584" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N584" s="30"/>
+      <c r="N584" s="27"/>
     </row>
     <row r="585" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N585" s="30"/>
+      <c r="N585" s="27"/>
     </row>
     <row r="586" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N586" s="30"/>
+      <c r="N586" s="27"/>
     </row>
     <row r="587" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N587" s="30"/>
+      <c r="N587" s="27"/>
     </row>
     <row r="588" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N588" s="30"/>
+      <c r="N588" s="27"/>
     </row>
     <row r="589" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N589" s="30"/>
+      <c r="N589" s="27"/>
     </row>
     <row r="590" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N590" s="30"/>
+      <c r="N590" s="27"/>
     </row>
     <row r="591" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N591" s="30"/>
+      <c r="N591" s="27"/>
     </row>
     <row r="592" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N592" s="30"/>
+      <c r="N592" s="27"/>
     </row>
     <row r="593" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N593" s="30"/>
+      <c r="N593" s="27"/>
     </row>
     <row r="594" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N594" s="30"/>
+      <c r="N594" s="27"/>
     </row>
     <row r="595" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N595" s="30"/>
+      <c r="N595" s="27"/>
     </row>
     <row r="596" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N596" s="30"/>
+      <c r="N596" s="27"/>
     </row>
     <row r="597" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N597" s="30"/>
+      <c r="N597" s="27"/>
     </row>
     <row r="598" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N598" s="30"/>
+      <c r="N598" s="27"/>
     </row>
     <row r="599" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N599" s="30"/>
+      <c r="N599" s="27"/>
     </row>
     <row r="600" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N600" s="30"/>
+      <c r="N600" s="27"/>
     </row>
     <row r="601" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N601" s="30"/>
+      <c r="N601" s="27"/>
     </row>
     <row r="602" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N602" s="30"/>
+      <c r="N602" s="27"/>
     </row>
     <row r="603" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N603" s="30"/>
+      <c r="N603" s="27"/>
     </row>
     <row r="604" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N604" s="30"/>
+      <c r="N604" s="27"/>
     </row>
     <row r="605" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N605" s="30"/>
+      <c r="N605" s="27"/>
     </row>
     <row r="606" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N606" s="30"/>
+      <c r="N606" s="27"/>
     </row>
     <row r="607" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N607" s="30"/>
+      <c r="N607" s="27"/>
     </row>
     <row r="608" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N608" s="30"/>
+      <c r="N608" s="27"/>
     </row>
     <row r="609" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N609" s="30"/>
+      <c r="N609" s="27"/>
     </row>
     <row r="610" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N610" s="30"/>
+      <c r="N610" s="27"/>
     </row>
     <row r="611" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N611" s="30"/>
+      <c r="N611" s="27"/>
     </row>
     <row r="612" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N612" s="30"/>
+      <c r="N612" s="27"/>
     </row>
     <row r="613" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N613" s="30"/>
+      <c r="N613" s="27"/>
     </row>
     <row r="614" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N614" s="30"/>
+      <c r="N614" s="27"/>
     </row>
     <row r="615" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N615" s="30"/>
+      <c r="N615" s="27"/>
     </row>
     <row r="616" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N616" s="30"/>
+      <c r="N616" s="27"/>
     </row>
     <row r="617" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N617" s="30"/>
+      <c r="N617" s="27"/>
     </row>
     <row r="618" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N618" s="30"/>
+      <c r="N618" s="27"/>
     </row>
     <row r="619" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N619" s="30"/>
+      <c r="N619" s="27"/>
     </row>
     <row r="620" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N620" s="30"/>
+      <c r="N620" s="27"/>
     </row>
     <row r="621" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N621" s="30"/>
+      <c r="N621" s="27"/>
     </row>
     <row r="622" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N622" s="30"/>
+      <c r="N622" s="27"/>
     </row>
     <row r="623" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N623" s="30"/>
+      <c r="N623" s="27"/>
     </row>
     <row r="624" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N624" s="30"/>
+      <c r="N624" s="27"/>
     </row>
     <row r="625" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N625" s="30"/>
+      <c r="N625" s="27"/>
     </row>
     <row r="626" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N626" s="30"/>
+      <c r="N626" s="27"/>
     </row>
     <row r="627" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N627" s="30"/>
+      <c r="N627" s="27"/>
     </row>
     <row r="628" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N628" s="30"/>
+      <c r="N628" s="27"/>
     </row>
     <row r="629" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N629" s="30"/>
+      <c r="N629" s="27"/>
     </row>
     <row r="630" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N630" s="30"/>
+      <c r="N630" s="27"/>
     </row>
     <row r="631" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N631" s="30"/>
+      <c r="N631" s="27"/>
     </row>
     <row r="632" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N632" s="30"/>
+      <c r="N632" s="27"/>
     </row>
     <row r="633" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N633" s="30"/>
+      <c r="N633" s="27"/>
     </row>
     <row r="634" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N634" s="30"/>
+      <c r="N634" s="27"/>
     </row>
     <row r="635" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N635" s="30"/>
+      <c r="N635" s="27"/>
     </row>
     <row r="636" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N636" s="30"/>
+      <c r="N636" s="27"/>
     </row>
     <row r="637" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N637" s="30"/>
+      <c r="N637" s="27"/>
     </row>
     <row r="638" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N638" s="30"/>
+      <c r="N638" s="27"/>
     </row>
     <row r="639" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N639" s="30"/>
+      <c r="N639" s="27"/>
     </row>
     <row r="640" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N640" s="30"/>
+      <c r="N640" s="27"/>
     </row>
     <row r="641" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N641" s="30"/>
+      <c r="N641" s="27"/>
     </row>
     <row r="642" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N642" s="30"/>
+      <c r="N642" s="27"/>
     </row>
     <row r="643" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N643" s="30"/>
+      <c r="N643" s="27"/>
     </row>
     <row r="644" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N644" s="30"/>
+      <c r="N644" s="27"/>
     </row>
     <row r="645" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N645" s="30"/>
+      <c r="N645" s="27"/>
     </row>
     <row r="646" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N646" s="30"/>
+      <c r="N646" s="27"/>
     </row>
     <row r="647" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N647" s="30"/>
+      <c r="N647" s="27"/>
     </row>
     <row r="648" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N648" s="30"/>
+      <c r="N648" s="27"/>
     </row>
     <row r="649" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N649" s="30"/>
+      <c r="N649" s="27"/>
     </row>
     <row r="650" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N650" s="30"/>
+      <c r="N650" s="27"/>
     </row>
     <row r="651" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N651" s="30"/>
+      <c r="N651" s="27"/>
     </row>
     <row r="652" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N652" s="30"/>
+      <c r="N652" s="27"/>
     </row>
     <row r="653" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N653" s="30"/>
+      <c r="N653" s="27"/>
     </row>
     <row r="654" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N654" s="30"/>
+      <c r="N654" s="27"/>
     </row>
     <row r="655" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N655" s="30"/>
+      <c r="N655" s="27"/>
     </row>
     <row r="656" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N656" s="30"/>
+      <c r="N656" s="27"/>
     </row>
     <row r="657" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N657" s="30"/>
+      <c r="N657" s="27"/>
     </row>
     <row r="658" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N658" s="30"/>
+      <c r="N658" s="27"/>
     </row>
     <row r="659" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N659" s="30"/>
+      <c r="N659" s="27"/>
     </row>
     <row r="660" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N660" s="30"/>
+      <c r="N660" s="27"/>
     </row>
     <row r="661" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N661" s="30"/>
+      <c r="N661" s="27"/>
     </row>
     <row r="662" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N662" s="30"/>
+      <c r="N662" s="27"/>
     </row>
     <row r="663" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N663" s="30"/>
+      <c r="N663" s="27"/>
     </row>
     <row r="664" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N664" s="30"/>
+      <c r="N664" s="27"/>
     </row>
     <row r="665" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N665" s="30"/>
+      <c r="N665" s="27"/>
     </row>
     <row r="666" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N666" s="30"/>
+      <c r="N666" s="27"/>
     </row>
     <row r="667" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N667" s="30"/>
+      <c r="N667" s="27"/>
     </row>
     <row r="668" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N668" s="30"/>
+      <c r="N668" s="27"/>
     </row>
     <row r="669" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N669" s="30"/>
+      <c r="N669" s="27"/>
     </row>
     <row r="670" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N670" s="30"/>
+      <c r="N670" s="27"/>
     </row>
     <row r="671" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N671" s="30"/>
+      <c r="N671" s="27"/>
     </row>
     <row r="672" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N672" s="30"/>
+      <c r="N672" s="27"/>
     </row>
     <row r="673" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N673" s="30"/>
+      <c r="N673" s="27"/>
     </row>
     <row r="674" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N674" s="30"/>
+      <c r="N674" s="27"/>
     </row>
     <row r="675" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N675" s="30"/>
+      <c r="N675" s="27"/>
     </row>
     <row r="676" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N676" s="30"/>
+      <c r="N676" s="27"/>
     </row>
     <row r="677" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N677" s="30"/>
+      <c r="N677" s="27"/>
     </row>
     <row r="678" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N678" s="30"/>
+      <c r="N678" s="27"/>
     </row>
     <row r="679" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N679" s="30"/>
+      <c r="N679" s="27"/>
     </row>
     <row r="680" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N680" s="30"/>
+      <c r="N680" s="27"/>
     </row>
     <row r="681" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N681" s="30"/>
+      <c r="N681" s="27"/>
     </row>
     <row r="682" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N682" s="30"/>
+      <c r="N682" s="27"/>
     </row>
     <row r="683" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N683" s="30"/>
+      <c r="N683" s="27"/>
     </row>
     <row r="684" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N684" s="30"/>
+      <c r="N684" s="27"/>
     </row>
     <row r="685" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N685" s="30"/>
+      <c r="N685" s="27"/>
     </row>
     <row r="686" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N686" s="30"/>
+      <c r="N686" s="27"/>
     </row>
     <row r="687" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N687" s="30"/>
+      <c r="N687" s="27"/>
     </row>
     <row r="688" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N688" s="30"/>
+      <c r="N688" s="27"/>
     </row>
     <row r="689" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N689" s="30"/>
+      <c r="N689" s="27"/>
     </row>
     <row r="690" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N690" s="30"/>
+      <c r="N690" s="27"/>
     </row>
     <row r="691" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N691" s="30"/>
+      <c r="N691" s="27"/>
     </row>
     <row r="692" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N692" s="30"/>
+      <c r="N692" s="27"/>
     </row>
     <row r="693" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N693" s="30"/>
+      <c r="N693" s="27"/>
     </row>
     <row r="694" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N694" s="30"/>
+      <c r="N694" s="27"/>
     </row>
     <row r="695" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N695" s="30"/>
+      <c r="N695" s="27"/>
     </row>
     <row r="696" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N696" s="30"/>
+      <c r="N696" s="27"/>
     </row>
     <row r="697" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N697" s="30"/>
+      <c r="N697" s="27"/>
     </row>
     <row r="698" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N698" s="30"/>
+      <c r="N698" s="27"/>
     </row>
     <row r="699" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N699" s="30"/>
+      <c r="N699" s="27"/>
     </row>
     <row r="700" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N700" s="30"/>
+      <c r="N700" s="27"/>
     </row>
     <row r="701" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N701" s="30"/>
+      <c r="N701" s="27"/>
     </row>
     <row r="702" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N702" s="30"/>
+      <c r="N702" s="27"/>
     </row>
     <row r="703" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N703" s="30"/>
+      <c r="N703" s="27"/>
     </row>
     <row r="704" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N704" s="30"/>
+      <c r="N704" s="27"/>
     </row>
     <row r="705" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N705" s="30"/>
+      <c r="N705" s="27"/>
     </row>
     <row r="706" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N706" s="30"/>
+      <c r="N706" s="27"/>
     </row>
     <row r="707" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N707" s="30"/>
+      <c r="N707" s="27"/>
     </row>
     <row r="708" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N708" s="30"/>
+      <c r="N708" s="27"/>
     </row>
     <row r="709" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N709" s="30"/>
+      <c r="N709" s="27"/>
     </row>
     <row r="710" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N710" s="30"/>
+      <c r="N710" s="27"/>
     </row>
     <row r="711" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N711" s="30"/>
+      <c r="N711" s="27"/>
     </row>
     <row r="712" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N712" s="30"/>
+      <c r="N712" s="27"/>
     </row>
     <row r="713" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N713" s="30"/>
+      <c r="N713" s="27"/>
     </row>
     <row r="714" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N714" s="30"/>
+      <c r="N714" s="27"/>
     </row>
     <row r="715" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N715" s="30"/>
+      <c r="N715" s="27"/>
     </row>
     <row r="716" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N716" s="30"/>
+      <c r="N716" s="27"/>
     </row>
     <row r="717" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N717" s="30"/>
+      <c r="N717" s="27"/>
     </row>
     <row r="718" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N718" s="30"/>
+      <c r="N718" s="27"/>
     </row>
     <row r="719" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N719" s="30"/>
+      <c r="N719" s="27"/>
     </row>
     <row r="720" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N720" s="30"/>
+      <c r="N720" s="27"/>
     </row>
     <row r="721" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N721" s="30"/>
+      <c r="N721" s="27"/>
     </row>
     <row r="722" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N722" s="30"/>
+      <c r="N722" s="27"/>
     </row>
     <row r="723" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N723" s="30"/>
+      <c r="N723" s="27"/>
     </row>
     <row r="724" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N724" s="30"/>
+      <c r="N724" s="27"/>
     </row>
     <row r="725" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N725" s="30"/>
+      <c r="N725" s="27"/>
     </row>
     <row r="726" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N726" s="30"/>
+      <c r="N726" s="27"/>
     </row>
     <row r="727" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N727" s="30"/>
+      <c r="N727" s="27"/>
     </row>
     <row r="728" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N728" s="30"/>
+      <c r="N728" s="27"/>
     </row>
     <row r="729" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N729" s="30"/>
+      <c r="N729" s="27"/>
     </row>
     <row r="730" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N730" s="30"/>
+      <c r="N730" s="27"/>
     </row>
     <row r="731" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N731" s="30"/>
+      <c r="N731" s="27"/>
     </row>
     <row r="732" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N732" s="30"/>
+      <c r="N732" s="27"/>
     </row>
     <row r="733" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N733" s="30"/>
+      <c r="N733" s="27"/>
     </row>
     <row r="734" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N734" s="30"/>
+      <c r="N734" s="27"/>
     </row>
     <row r="735" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N735" s="30"/>
+      <c r="N735" s="27"/>
     </row>
     <row r="736" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N736" s="30"/>
+      <c r="N736" s="27"/>
     </row>
     <row r="737" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N737" s="30"/>
+      <c r="N737" s="27"/>
     </row>
     <row r="738" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N738" s="30"/>
+      <c r="N738" s="27"/>
     </row>
     <row r="739" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N739" s="30"/>
+      <c r="N739" s="27"/>
     </row>
     <row r="740" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N740" s="30"/>
+      <c r="N740" s="27"/>
     </row>
     <row r="741" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N741" s="30"/>
+      <c r="N741" s="27"/>
     </row>
     <row r="742" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N742" s="30"/>
+      <c r="N742" s="27"/>
     </row>
     <row r="743" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N743" s="30"/>
+      <c r="N743" s="27"/>
     </row>
     <row r="744" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N744" s="30"/>
+      <c r="N744" s="27"/>
     </row>
     <row r="745" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N745" s="30"/>
+      <c r="N745" s="27"/>
     </row>
     <row r="746" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N746" s="30"/>
+      <c r="N746" s="27"/>
     </row>
     <row r="747" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N747" s="30"/>
+      <c r="N747" s="27"/>
     </row>
     <row r="748" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N748" s="30"/>
+      <c r="N748" s="27"/>
     </row>
     <row r="749" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N749" s="30"/>
+      <c r="N749" s="27"/>
     </row>
     <row r="750" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N750" s="30"/>
+      <c r="N750" s="27"/>
     </row>
     <row r="751" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N751" s="30"/>
+      <c r="N751" s="27"/>
     </row>
     <row r="752" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N752" s="30"/>
+      <c r="N752" s="27"/>
     </row>
     <row r="753" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N753" s="30"/>
+      <c r="N753" s="27"/>
     </row>
     <row r="754" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N754" s="30"/>
+      <c r="N754" s="27"/>
     </row>
     <row r="755" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N755" s="30"/>
+      <c r="N755" s="27"/>
     </row>
     <row r="756" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N756" s="30"/>
+      <c r="N756" s="27"/>
     </row>
     <row r="757" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N757" s="30"/>
+      <c r="N757" s="27"/>
     </row>
     <row r="758" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N758" s="30"/>
+      <c r="N758" s="27"/>
     </row>
     <row r="759" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N759" s="30"/>
+      <c r="N759" s="27"/>
     </row>
     <row r="760" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N760" s="30"/>
+      <c r="N760" s="27"/>
     </row>
     <row r="761" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N761" s="30"/>
+      <c r="N761" s="27"/>
     </row>
     <row r="762" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N762" s="30"/>
+      <c r="N762" s="27"/>
     </row>
     <row r="763" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N763" s="30"/>
+      <c r="N763" s="27"/>
     </row>
     <row r="764" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N764" s="30"/>
+      <c r="N764" s="27"/>
     </row>
     <row r="765" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N765" s="30"/>
+      <c r="N765" s="27"/>
     </row>
     <row r="766" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N766" s="30"/>
+      <c r="N766" s="27"/>
     </row>
     <row r="767" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N767" s="30"/>
+      <c r="N767" s="27"/>
     </row>
     <row r="768" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N768" s="30"/>
+      <c r="N768" s="27"/>
     </row>
     <row r="769" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N769" s="30"/>
+      <c r="N769" s="27"/>
     </row>
     <row r="770" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N770" s="30"/>
+      <c r="N770" s="27"/>
     </row>
     <row r="771" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N771" s="30"/>
+      <c r="N771" s="27"/>
     </row>
     <row r="772" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N772" s="30"/>
+      <c r="N772" s="27"/>
     </row>
     <row r="773" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N773" s="30"/>
+      <c r="N773" s="27"/>
     </row>
     <row r="774" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N774" s="30"/>
+      <c r="N774" s="27"/>
     </row>
     <row r="775" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N775" s="30"/>
+      <c r="N775" s="27"/>
     </row>
     <row r="776" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N776" s="30"/>
+      <c r="N776" s="27"/>
     </row>
     <row r="777" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N777" s="30"/>
+      <c r="N777" s="27"/>
     </row>
     <row r="778" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N778" s="30"/>
+      <c r="N778" s="27"/>
     </row>
     <row r="779" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N779" s="30"/>
+      <c r="N779" s="27"/>
     </row>
     <row r="780" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N780" s="30"/>
+      <c r="N780" s="27"/>
     </row>
     <row r="781" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N781" s="30"/>
+      <c r="N781" s="27"/>
     </row>
     <row r="782" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N782" s="30"/>
+      <c r="N782" s="27"/>
     </row>
     <row r="783" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N783" s="30"/>
+      <c r="N783" s="27"/>
     </row>
     <row r="784" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N784" s="30"/>
+      <c r="N784" s="27"/>
     </row>
     <row r="785" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N785" s="30"/>
+      <c r="N785" s="27"/>
     </row>
     <row r="786" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N786" s="30"/>
+      <c r="N786" s="27"/>
     </row>
     <row r="787" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N787" s="30"/>
+      <c r="N787" s="27"/>
     </row>
     <row r="788" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N788" s="30"/>
+      <c r="N788" s="27"/>
     </row>
     <row r="789" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N789" s="30"/>
+      <c r="N789" s="27"/>
     </row>
     <row r="790" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N790" s="30"/>
+      <c r="N790" s="27"/>
     </row>
     <row r="791" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N791" s="30"/>
+      <c r="N791" s="27"/>
     </row>
     <row r="792" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N792" s="30"/>
+      <c r="N792" s="27"/>
     </row>
     <row r="793" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N793" s="30"/>
+      <c r="N793" s="27"/>
     </row>
     <row r="794" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N794" s="30"/>
+      <c r="N794" s="27"/>
     </row>
     <row r="795" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N795" s="30"/>
+      <c r="N795" s="27"/>
     </row>
     <row r="796" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N796" s="30"/>
+      <c r="N796" s="27"/>
     </row>
     <row r="797" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N797" s="30"/>
+      <c r="N797" s="27"/>
     </row>
     <row r="798" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N798" s="30"/>
+      <c r="N798" s="27"/>
     </row>
     <row r="799" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N799" s="30"/>
+      <c r="N799" s="27"/>
     </row>
     <row r="800" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N800" s="30"/>
+      <c r="N800" s="27"/>
     </row>
     <row r="801" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N801" s="30"/>
+      <c r="N801" s="27"/>
     </row>
     <row r="802" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N802" s="30"/>
+      <c r="N802" s="27"/>
     </row>
     <row r="803" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N803" s="30"/>
+      <c r="N803" s="27"/>
     </row>
     <row r="804" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N804" s="30"/>
+      <c r="N804" s="27"/>
     </row>
     <row r="805" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N805" s="30"/>
+      <c r="N805" s="27"/>
     </row>
     <row r="806" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N806" s="30"/>
+      <c r="N806" s="27"/>
     </row>
     <row r="807" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N807" s="30"/>
+      <c r="N807" s="27"/>
     </row>
     <row r="808" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N808" s="30"/>
+      <c r="N808" s="27"/>
     </row>
     <row r="809" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N809" s="30"/>
+      <c r="N809" s="27"/>
     </row>
     <row r="810" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N810" s="30"/>
+      <c r="N810" s="27"/>
     </row>
     <row r="811" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N811" s="30"/>
+      <c r="N811" s="27"/>
     </row>
     <row r="812" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N812" s="30"/>
+      <c r="N812" s="27"/>
     </row>
     <row r="813" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N813" s="30"/>
+      <c r="N813" s="27"/>
     </row>
     <row r="814" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N814" s="30"/>
+      <c r="N814" s="27"/>
     </row>
     <row r="815" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N815" s="30"/>
+      <c r="N815" s="27"/>
     </row>
     <row r="816" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N816" s="30"/>
+      <c r="N816" s="27"/>
     </row>
     <row r="817" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N817" s="30"/>
+      <c r="N817" s="27"/>
     </row>
     <row r="818" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N818" s="30"/>
+      <c r="N818" s="27"/>
     </row>
     <row r="819" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N819" s="30"/>
+      <c r="N819" s="27"/>
     </row>
     <row r="820" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N820" s="30"/>
+      <c r="N820" s="27"/>
     </row>
     <row r="821" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N821" s="30"/>
+      <c r="N821" s="27"/>
     </row>
     <row r="822" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N822" s="30"/>
+      <c r="N822" s="27"/>
     </row>
     <row r="823" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N823" s="30"/>
+      <c r="N823" s="27"/>
     </row>
     <row r="824" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N824" s="30"/>
+      <c r="N824" s="27"/>
     </row>
     <row r="825" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N825" s="30"/>
+      <c r="N825" s="27"/>
     </row>
     <row r="826" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N826" s="30"/>
+      <c r="N826" s="27"/>
     </row>
     <row r="827" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N827" s="30"/>
+      <c r="N827" s="27"/>
     </row>
     <row r="828" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N828" s="30"/>
+      <c r="N828" s="27"/>
     </row>
     <row r="829" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N829" s="30"/>
+      <c r="N829" s="27"/>
     </row>
     <row r="830" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N830" s="30"/>
+      <c r="N830" s="27"/>
     </row>
     <row r="831" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N831" s="30"/>
+      <c r="N831" s="27"/>
     </row>
     <row r="832" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N832" s="30"/>
+      <c r="N832" s="27"/>
     </row>
     <row r="833" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N833" s="30"/>
+      <c r="N833" s="27"/>
     </row>
     <row r="834" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N834" s="30"/>
+      <c r="N834" s="27"/>
     </row>
     <row r="835" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N835" s="30"/>
+      <c r="N835" s="27"/>
     </row>
     <row r="836" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N836" s="30"/>
+      <c r="N836" s="27"/>
     </row>
     <row r="837" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N837" s="30"/>
+      <c r="N837" s="27"/>
     </row>
     <row r="838" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N838" s="30"/>
+      <c r="N838" s="27"/>
     </row>
     <row r="839" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N839" s="30"/>
+      <c r="N839" s="27"/>
     </row>
     <row r="840" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N840" s="30"/>
+      <c r="N840" s="27"/>
     </row>
     <row r="841" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N841" s="30"/>
+      <c r="N841" s="27"/>
     </row>
     <row r="842" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N842" s="30"/>
+      <c r="N842" s="27"/>
     </row>
     <row r="843" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N843" s="30"/>
+      <c r="N843" s="27"/>
     </row>
     <row r="844" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N844" s="30"/>
+      <c r="N844" s="27"/>
     </row>
     <row r="845" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N845" s="30"/>
+      <c r="N845" s="27"/>
     </row>
     <row r="846" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N846" s="30"/>
+      <c r="N846" s="27"/>
     </row>
     <row r="847" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N847" s="30"/>
+      <c r="N847" s="27"/>
     </row>
     <row r="848" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N848" s="30"/>
+      <c r="N848" s="27"/>
     </row>
     <row r="849" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N849" s="30"/>
+      <c r="N849" s="27"/>
     </row>
     <row r="850" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N850" s="30"/>
+      <c r="N850" s="27"/>
     </row>
     <row r="851" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N851" s="30"/>
+      <c r="N851" s="27"/>
     </row>
     <row r="852" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N852" s="30"/>
+      <c r="N852" s="27"/>
     </row>
     <row r="853" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N853" s="30"/>
+      <c r="N853" s="27"/>
     </row>
     <row r="854" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N854" s="30"/>
+      <c r="N854" s="27"/>
     </row>
     <row r="855" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N855" s="30"/>
+      <c r="N855" s="27"/>
     </row>
     <row r="856" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N856" s="30"/>
+      <c r="N856" s="27"/>
     </row>
     <row r="857" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N857" s="30"/>
+      <c r="N857" s="27"/>
     </row>
     <row r="858" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N858" s="30"/>
+      <c r="N858" s="27"/>
     </row>
     <row r="859" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N859" s="30"/>
+      <c r="N859" s="27"/>
     </row>
     <row r="860" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N860" s="30"/>
+      <c r="N860" s="27"/>
     </row>
     <row r="861" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N861" s="30"/>
+      <c r="N861" s="27"/>
     </row>
     <row r="862" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N862" s="30"/>
+      <c r="N862" s="27"/>
     </row>
     <row r="863" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N863" s="30"/>
+      <c r="N863" s="27"/>
     </row>
     <row r="864" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N864" s="30"/>
+      <c r="N864" s="27"/>
     </row>
     <row r="865" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N865" s="30"/>
+      <c r="N865" s="27"/>
     </row>
     <row r="866" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N866" s="30"/>
+      <c r="N866" s="27"/>
     </row>
     <row r="867" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N867" s="30"/>
+      <c r="N867" s="27"/>
     </row>
     <row r="868" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N868" s="30"/>
+      <c r="N868" s="27"/>
     </row>
     <row r="869" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N869" s="30"/>
+      <c r="N869" s="27"/>
     </row>
     <row r="870" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N870" s="30"/>
+      <c r="N870" s="27"/>
     </row>
     <row r="871" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N871" s="30"/>
+      <c r="N871" s="27"/>
     </row>
     <row r="872" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N872" s="30"/>
+      <c r="N872" s="27"/>
     </row>
     <row r="873" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N873" s="30"/>
+      <c r="N873" s="27"/>
     </row>
     <row r="874" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N874" s="30"/>
+      <c r="N874" s="27"/>
     </row>
     <row r="875" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N875" s="30"/>
+      <c r="N875" s="27"/>
     </row>
     <row r="876" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N876" s="30"/>
+      <c r="N876" s="27"/>
     </row>
     <row r="877" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N877" s="30"/>
+      <c r="N877" s="27"/>
     </row>
     <row r="878" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N878" s="30"/>
+      <c r="N878" s="27"/>
     </row>
     <row r="879" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N879" s="30"/>
+      <c r="N879" s="27"/>
     </row>
     <row r="880" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N880" s="30"/>
+      <c r="N880" s="27"/>
     </row>
     <row r="881" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N881" s="30"/>
+      <c r="N881" s="27"/>
     </row>
     <row r="882" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N882" s="30"/>
+      <c r="N882" s="27"/>
     </row>
     <row r="883" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N883" s="30"/>
+      <c r="N883" s="27"/>
     </row>
     <row r="884" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N884" s="30"/>
+      <c r="N884" s="27"/>
     </row>
     <row r="885" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N885" s="30"/>
+      <c r="N885" s="27"/>
     </row>
     <row r="886" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N886" s="30"/>
+      <c r="N886" s="27"/>
     </row>
     <row r="887" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N887" s="30"/>
+      <c r="N887" s="27"/>
     </row>
     <row r="888" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N888" s="30"/>
+      <c r="N888" s="27"/>
     </row>
     <row r="889" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N889" s="30"/>
+      <c r="N889" s="27"/>
     </row>
     <row r="890" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N890" s="30"/>
+      <c r="N890" s="27"/>
     </row>
     <row r="891" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N891" s="30"/>
+      <c r="N891" s="27"/>
     </row>
     <row r="892" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N892" s="30"/>
+      <c r="N892" s="27"/>
     </row>
     <row r="893" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N893" s="30"/>
+      <c r="N893" s="27"/>
     </row>
     <row r="894" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N894" s="30"/>
+      <c r="N894" s="27"/>
     </row>
     <row r="895" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N895" s="30"/>
+      <c r="N895" s="27"/>
     </row>
     <row r="896" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N896" s="30"/>
+      <c r="N896" s="27"/>
     </row>
     <row r="897" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N897" s="30"/>
+      <c r="N897" s="27"/>
     </row>
     <row r="898" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N898" s="30"/>
+      <c r="N898" s="27"/>
     </row>
     <row r="899" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N899" s="30"/>
+      <c r="N899" s="27"/>
     </row>
     <row r="900" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N900" s="30"/>
+      <c r="N900" s="27"/>
     </row>
     <row r="901" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N901" s="30"/>
+      <c r="N901" s="27"/>
     </row>
     <row r="902" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N902" s="30"/>
+      <c r="N902" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="1">
